--- a/JsonConverter/ExcelFiles/OO_Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Dialogue.xlsx
@@ -12,14 +12,14 @@
   <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="zgynNiv2YVTupuAxVwKvj3LXvSi69gCaqo2XUeu/LZo="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="" roundtripDataChecksum="zgynNiv2YVTupuAxVwKvj3LXvSi69gCaqo2XUeu/LZo="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
@@ -62,31 +62,86 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
+    <t>모란</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillList</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>"치.직... 시.스.템. 가.동. 아.버.지! 저. 말.도. 하.고. 움.직.여.요. 가.슴.속. 태.엽.이. 진짜. 심.장. 처.럼. 쿵.쾅.거.립.니.다. 소.녀. 다.시. 인.사. 올.려.드.리.옵.니.다."</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>장영심</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>“……장, 장금아……! 네가 정녕 돌아온 것이냐……!”</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_JangYoungSim_01</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Mr.Jaeik_01</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>재익군</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>"끄응…! 어이쿠, 이 맛은 당최 무엇이구멍유?! 가슴 깊은 곳에서 뜨거운 기운이 확 솟구치는구멍! ……어라? 내, 내가 왜 두 발로 서 있는 거래유? 게다가 사람 말이 입 밖으로 막 나오잖습지멍?! 아이고 대감 천지신명이시여, 이게 무슨 기적이란 말이멍유!"</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Chunyang_01</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>춘양</t>
+  </si>
+  <si>
+    <t>춘양</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>“재익아! 네 이놈, 어디 갔나 했더니 여기서 뭘 먹고…… 아니, 네가 어찌 사람의 옷을 입고 두 발로 서 있는 게냐? 귀신이 곡할 노릇이로구나!”</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Mr.Jaeik_02</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>“아씨! 글쎄 이 신비로운 요리를 한 입 먹었더니만, 온몸의 털이 곤두서며 진짜로 말하는 사람이 되었구멍요!”</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <t>character_Moran_01</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
+    <t>character_Moran_02</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <t>모란</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>SkillList</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>"치.직... 시.스.템. 가.동. 아.버.지! 저. 말.도. 하.고. 움.직.여.요. 가.슴.속. 태.엽.이. 진짜. 심.장. 처.럼. 쿵.쾅.거.립.니.다. 소.녀. 다.시. 인.사. 올.려.드.리.옵.니.다."</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>character_JangYoungSim_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>장영심</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>“……장, 장금아……! 네가 정녕 돌아온 것이냐……!”</t>
+    <t>“안녕하세요, 여러분! 음식으로 세상을 치유하는 멋진 여정을 떠나보려고 해요. 제 동료가 되어서 이 모험을 함께해 주시지 않겠어요?”</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Chunyang_02</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>“나는 홀연히 자취를 감춘 서방님, 몽령 나으리를 찾기 위해 온 팔도를 헤매는 중이라오. 갈 길이 멀고 험난한 여정이 되겠으나…… 그대들의 이 신비로운 음식을 여정 내내 맛볼 수만 있다면, 내 기꺼이 길잡이가 되어 드리겠소.”</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -549,7 +604,7 @@
         <v>6</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>10</v>
@@ -560,13 +615,13 @@
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>13</v>
-      </c>
       <c r="C4" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
@@ -583,13 +638,13 @@
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>16</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>18</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -605,9 +660,15 @@
       <c r="O5" s="5"/>
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
+      <c r="A6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -622,9 +683,15 @@
       <c r="O6" s="5"/>
     </row>
     <row r="7" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
+      <c r="A7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>24</v>
+      </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -639,9 +706,15 @@
       <c r="O7" s="5"/>
     </row>
     <row r="8" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
+      <c r="A8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
@@ -656,9 +729,15 @@
       <c r="O8" s="5"/>
     </row>
     <row r="9" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
+      <c r="A9" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>30</v>
+      </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
@@ -673,9 +752,15 @@
       <c r="O9" s="5"/>
     </row>
     <row r="10" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
+      <c r="A10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>

--- a/JsonConverter/ExcelFiles/OO_Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Dialogue.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="54">
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
@@ -86,11 +86,81 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
+    <t>재익군</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Chunyang_01</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>춘양</t>
+  </si>
+  <si>
+    <t>춘양</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Mr.Jaeik_02</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Moran_01</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>모란</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Chunyang_02</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Chunyang_03</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>춘양</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>“나는 홀연히 자취를 감춘 서방님, 몽령 나으리를 찾기 위해 온 팔도를 헤매는 중이라오. 갈 길이 멀고 험난한 여정이 되겠으나…… 그대들의 이 신비로운 음식을 여정 내내 맛볼 수만 있다면, 내 기꺼이 길잡이가 되어 드리겠소.”</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>“재익아! 네 이놈, 어디 갔나 했더니 여기서 뭘 먹고…… 아니, 네가 어찌 사람의 옷을 입고 두 발로 서 있는 게냐? 귀신이 곡할 노릇이로구나!”</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>“우리 아버님께서 내어주신 참으로 귀한 쌀이라오. 자네들의 여정에 조금이나마 보탬이 되었으면 좋겠소.”</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Moran_02</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>모란</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>“안녕하세요, 여러분! 음식으로 세상을 치유하는 멋진 여정을 떠나보려고 해요. 제 동료가 되어서 이 모험을 함께해 주시지 않겠어요?”</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <t>character_Mr.Jaeik_01</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>재익군</t>
+  </si>
+  <si>
+    <t>재익군</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>“우리 집 마당에서 기른 귀한 채소들이에요. 참 맛좋은 음식들이 가득했었는데… 아쉽게도 다른 음식은 재익 군이 남김없이 다 먹어버렸지요! 하하.”</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -98,50 +168,1279 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>character_Chunyang_01</t>
+    <t>“아씨! 글쎄 이 신비로운 요리를 한 입 먹었더니만, 온몸의 털이 곤두서며 진짜로 말하는 사람이 되었구멍요!”</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>“아이고, 모란님… 면목이 없구멍유. 그 참을 수 없는 냄새에 저도 모르게 개 버릇을 못 고치고 주둥이가 먼저 나가버렸지 멍유……. 정말 미안하구멍유…….”</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>모란님</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>미련한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>놈의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>허물은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>대신</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사죄하겠소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>밥값을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>하려면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>부지런히</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>길을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>나서야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>터</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">…… </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>먼저는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>동쪽으로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>가시지요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>그곳에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>탐관오리의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>수탈로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>배</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>굶주린</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>자들이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>유독</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>많다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>들었습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>”</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Chunyang_04</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Mr.Jaeik_03</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Mr.Jaeik_04</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Chunyang_05</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Moran_03</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>“슬슬 날이 저무니 배가 고프지 않습니까요, 아씨? 제가 배고파서 그런 건 절대 아니구멍유……! 모란 님이 우리를 위해 맛난 요리를 해주신다면 참말로 감사하겠서요!”
+(그의 꼬리를 흔들리는걸 멈추지 않는 탓일가)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그러고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보니</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>벌써</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>저녁때가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>되었구려</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마침</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다들</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지쳤을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>터인데</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>낭자에게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>염치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>불고하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>따뜻한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>식사를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부탁드려도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>되겠소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>?”</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>당연히</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>해드려야죠</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가마솥을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뜨겁게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>달굴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>테니</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>두</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>분</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>조금만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기다려주세요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>세상에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>배부른</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>요리를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지어드릴게요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>!”</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Moran_04</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>모란</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>춘양</t>
-  </si>
-  <si>
-    <t>춘양</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>“재익아! 네 이놈, 어디 갔나 했더니 여기서 뭘 먹고…… 아니, 네가 어찌 사람의 옷을 입고 두 발로 서 있는 게냐? 귀신이 곡할 노릇이로구나!”</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>character_Mr.Jaeik_02</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>“아씨! 글쎄 이 신비로운 요리를 한 입 먹었더니만, 온몸의 털이 곤두서며 진짜로 말하는 사람이 되었구멍요!”</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>character_Moran_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>character_Moran_02</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>모란</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>“안녕하세요, 여러분! 음식으로 세상을 치유하는 멋진 여정을 떠나보려고 해요. 제 동료가 되어서 이 모험을 함께해 주시지 않겠어요?”</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>character_Chunyang_02</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>“나는 홀연히 자취를 감춘 서방님, 몽령 나으리를 찾기 위해 온 팔도를 헤매는 중이라오. 갈 길이 멀고 험난한 여정이 되겠으나…… 그대들의 이 신비로운 음식을 여정 내내 맛볼 수만 있다면, 내 기꺼이 길잡이가 되어 드리겠소.”</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>재익군</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -149,7 +1448,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="9">
+  <fonts count="13">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -210,6 +1509,37 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="8">
@@ -298,7 +1628,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -328,6 +1658,12 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -615,7 +1951,7 @@
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>12</v>
@@ -661,13 +1997,13 @@
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1">
       <c r="A6" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>19</v>
-      </c>
       <c r="C6" s="6" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
@@ -684,13 +2020,13 @@
     </row>
     <row r="7" spans="1:15" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>23</v>
-      </c>
       <c r="C7" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
@@ -707,13 +2043,13 @@
     </row>
     <row r="8" spans="1:15" ht="15.75" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
@@ -730,13 +2066,13 @@
     </row>
     <row r="9" spans="1:15" ht="15.75" customHeight="1">
       <c r="A9" s="7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
@@ -753,13 +2089,13 @@
     </row>
     <row r="10" spans="1:15" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
@@ -775,9 +2111,15 @@
       <c r="O10" s="5"/>
     </row>
     <row r="11" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
+      <c r="A11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
@@ -792,9 +2134,15 @@
       <c r="O11" s="5"/>
     </row>
     <row r="12" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
+      <c r="A12" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>37</v>
+      </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
@@ -809,9 +2157,15 @@
       <c r="O12" s="5"/>
     </row>
     <row r="13" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
+      <c r="A13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>40</v>
+      </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
@@ -826,9 +2180,15 @@
       <c r="O13" s="5"/>
     </row>
     <row r="14" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
+      <c r="A14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>41</v>
+      </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
@@ -843,9 +2203,15 @@
       <c r="O14" s="5"/>
     </row>
     <row r="15" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
+      <c r="A15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>47</v>
+      </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
@@ -860,14 +2226,26 @@
       <c r="O15" s="5"/>
     </row>
     <row r="16" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
+      <c r="A16" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
+      <c r="A17" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="18" spans="1:5" ht="15.75" customHeight="1">
       <c r="A18" s="9"/>

--- a/JsonConverter/ExcelFiles/OO_Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Dialogue.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="57">
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
@@ -1428,19 +1428,280 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
+    <t>춘양</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>재익군</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <t>character_Moran_04</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
+    <t>character_Moran_05</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <t>모란</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>춘양</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>재익군</t>
+    <t>모란</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>따끈따끈한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ‘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>야채죽</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>’</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>완성되었어요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>소박하지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지친</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>몸을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>따뜻하게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>데워줄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>거예요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>맛있게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>드세요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>!”</t>
+    </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -2207,7 +2468,7 @@
         <v>44</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C15" s="18" t="s">
         <v>47</v>
@@ -2230,7 +2491,7 @@
         <v>45</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>48</v>
@@ -2238,19 +2499,25 @@
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1">
       <c r="A17" s="9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
+      <c r="A18" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="19" spans="1:5" ht="15.75" customHeight="1">
       <c r="A19" s="9"/>

--- a/JsonConverter/ExcelFiles/OO_Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Dialogue.xlsx
@@ -1,121 +1,1655 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="12770" yWindow="2240" windowWidth="19820" windowHeight="18420" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="12770" yWindow="2240" windowWidth="19820" windowHeight="18420"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DNTable_Dialogue" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="DNTable_Dialogue" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="56">
+  <si>
+    <t>대사 ID</t>
+  </si>
+  <si>
+    <t>화자 이름 또는 캐릭터 ID</t>
+  </si>
+  <si>
+    <t>대사 내용</t>
+  </si>
+  <si>
+    <t>다음 대사 ID</t>
+  </si>
+  <si>
+    <t>선택지 이름 목록(| 구분)</t>
+  </si>
+  <si>
+    <t>선택지 이동 대사 ID 목록(| 구분)</t>
+  </si>
+  <si>
+    <t>캐릭터 일러스트 경로</t>
+  </si>
+  <si>
+    <t>음성 파일 경로</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>SpeakerName</t>
+  </si>
+  <si>
+    <t>Text</t>
+  </si>
+  <si>
+    <t>NextDialogueId</t>
+  </si>
+  <si>
+    <t>SelectionNameList</t>
+  </si>
+  <si>
+    <t>SelectionDialogueIdList</t>
+  </si>
+  <si>
+    <t>TexturePath</t>
+  </si>
+  <si>
+    <t>VoicePath</t>
+  </si>
+  <si>
+    <t>character_Moran_01</t>
+  </si>
+  <si>
+    <t>모란</t>
+  </si>
+  <si>
+    <t>"치.직... 시.스.템. 가.동. 아.버.지! 저. 말.도. 하.고. 움.직.여.요. 가.슴.속. 태.엽.이. 진짜. 심.장. 처.럼. 쿵.쾅.거.립.니.다. 소.녀. 다.시. 인.사. 올.려.드.리.옵.니.다."</t>
+  </si>
+  <si>
+    <t>character_JangYoungSim_01</t>
+  </si>
+  <si>
+    <t>장영심</t>
+  </si>
+  <si>
+    <t>“……장, 장금아……! 네가 정녕 돌아온 것이냐……!”</t>
+  </si>
+  <si>
+    <t>character_Mr.Jaeik_01</t>
+  </si>
+  <si>
+    <t>재익군</t>
+  </si>
+  <si>
+    <t>"끄응…! 어이쿠, 이 맛은 당최 무엇이구멍유?! 가슴 깊은 곳에서 뜨거운 기운이 확 솟구치는구멍! ……어라? 내, 내가 왜 두 발로 서 있는 거래유? 게다가 사람 말이 입 밖으로 막 나오잖습지멍?! 아이고 대감 천지신명이시여, 이게 무슨 기적이란 말이멍유!"</t>
+  </si>
+  <si>
+    <t>character_Chunyang_01</t>
+  </si>
+  <si>
+    <t>춘양</t>
+  </si>
+  <si>
+    <t>“재익아! 네 이놈, 어디 갔나 했더니 여기서 뭘 먹고…… 아니, 네가 어찌 사람의 옷을 입고 두 발로 서 있는 게냐? 귀신이 곡할 노릇이로구나!”</t>
+  </si>
+  <si>
+    <t>character_Mr.Jaeik_02</t>
+  </si>
+  <si>
+    <t>“아씨! 글쎄 이 신비로운 요리를 한 입 먹었더니만, 온몸의 털이 곤두서며 진짜로 말하는 사람이 되었구멍요!”</t>
+  </si>
+  <si>
+    <t>character_Moran_02</t>
+  </si>
+  <si>
+    <t>“안녕하세요, 여러분! 음식으로 세상을 치유하는 멋진 여정을 떠나보려고 해요. 제 동료가 되어서 이 모험을 함께해 주시지 않겠어요?”</t>
+  </si>
+  <si>
+    <t>character_Chunyang_02</t>
+  </si>
+  <si>
+    <t>“나는 홀연히 자취를 감춘 서방님, 몽령 나으리를 찾기 위해 온 팔도를 헤매는 중이라오. 갈 길이 멀고 험난한 여정이 되겠으나…… 그대들의 이 신비로운 음식을 여정 내내 맛볼 수만 있다면, 내 기꺼이 길잡이가 되어 드리겠소.”</t>
+  </si>
+  <si>
+    <t>character_Chunyang_03</t>
+  </si>
+  <si>
+    <t>“우리 아버님께서 내어주신 참으로 귀한 쌀이라오. 자네들의 여정에 조금이나마 보탬이 되었으면 좋겠소.”</t>
+  </si>
+  <si>
+    <t>character_Moran_03</t>
+  </si>
+  <si>
+    <t>“우리 집 마당에서 기른 귀한 채소들이에요. 참 맛좋은 음식들이 가득했었는데… 아쉽게도 다른 음식은 재익 군이 남김없이 다 먹어버렸지요! 하하.”</t>
+  </si>
+  <si>
+    <t>character_Mr.Jaeik_03</t>
+  </si>
+  <si>
+    <t>“아이고, 모란님… 면목이 없구멍유. 그 참을 수 없는 냄새에 저도 모르게 개 버릇을 못 고치고 주둥이가 먼저 나가버렸지 멍유……. 정말 미안하구멍유…….”</t>
+  </si>
+  <si>
+    <t>character_Chunyang_04</t>
+  </si>
+  <si>
+    <t>“모란님, 이 미련한 놈의 허물은 내 대신 사죄하겠소. 밥값을 하려면 부지런히 길을 나서야 할 터…… 먼저는 동쪽으로 가시지요. 그곳에 탐관오리의 수탈로 배 굶주린 자들이 유독 많다 들었습니다.”</t>
+  </si>
+  <si>
+    <t>character_Mr.Jaeik_04</t>
+  </si>
+  <si>
+    <t>“슬슬 날이 저무니 배가 고프지 않습니까요, 아씨? 제가 배고파서 그런 건 절대 아니구멍유……! 모란 님이 우리를 위해 맛난 요리를 해주신다면 참말로 감사하겠서요!”
+(그의 꼬리를 흔들리는걸 멈추지 않는 탓일가)</t>
+  </si>
+  <si>
+    <t>character_Chunyang_05</t>
+  </si>
+  <si>
+    <t>“그러고 보니 벌써 저녁때가 되었구려. 마침 다들 지쳤을 터인데, 낭자에게 염치 불고하고 따뜻한 식사를 부탁드려도 되겠소?”</t>
+  </si>
+  <si>
+    <t>character_Moran_04</t>
+  </si>
+  <si>
+    <t>“당연히 해드려야죠! 가마솥을 뜨겁게 달굴 테니, 두 분 다 조금만 기다려주세요. 세상에서 가장 배부른 요리를 지어드릴게요!”</t>
+  </si>
+  <si>
+    <t>“따끈따끈한 ‘야채죽’이 완성되었어요! 소박하지만 지친 몸을 따뜻하게 데워줄 거예요. 어서 맛있게 드세요!”</t>
+  </si>
+  <si>
+    <r>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>포학한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>왕이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보낸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>탐관오리들이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가호마다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뼛속까지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수탈해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가니</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>우리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마을엔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>들쥐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>새끼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>먹을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>것조차</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>남지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않았소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>백성들이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>길가에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>쓰러져</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>굶어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>죽어가는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실정이오</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">……. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부디</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오늘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>단</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하루만이라도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지친</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이들의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주린</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>배를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>달래줄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>따뜻한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>온기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그릇을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나누어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>줄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없겠소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>?”</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Moran_05</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_VillageChief_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>촌장</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_VillageChief_02</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>허어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>눈물이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>앞을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가리는구려</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">…… </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>은혜를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어찌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>갚아야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>할지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모르겠소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지금은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>척박해진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>땅이나</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>매서운</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>추위도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잊게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>만드는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>우리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마을의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오랜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>특산물인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>청양고추라오</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모란님의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>앞날에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>작게나마</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보탬이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>되길</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바라오</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.”</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="14">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="9">
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="&quot;맑은 고딕&quot;"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="10"/>
     </font>
     <font>
-      <name val="&quot;맑은 고딕&quot;"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF008000"/>
-      <sz val="11"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
+      <sz val="8"/>
       <name val="Arial"/>
-      <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <sz val="8"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="맑은 고딕"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="돋움"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="돋움"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="돋움"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <color theme="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="돋움"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -146,29 +1680,23 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.7999816888943144"/>
-        <bgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.7999816888943144"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
+        <fgColor rgb="FFD9EAF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2F0D9"/>
+        <fgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -214,133 +1742,65 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="23">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -541,654 +2001,526 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:O1000"/>
+  <sheetFormatPr defaultColWidth="17" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="14" customWidth="1" style="3" min="1" max="1"/>
-    <col width="21" customWidth="1" style="3" min="2" max="2"/>
-    <col width="14" customWidth="1" style="3" min="3" max="3"/>
-    <col width="14" customWidth="1" style="3" min="4" max="4"/>
-    <col width="21" customWidth="1" style="3" min="5" max="5"/>
-    <col width="27" customWidth="1" style="3" min="6" max="6"/>
-    <col width="17" customWidth="1" style="3" min="7" max="16384"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col min="1" max="1" width="14" style="2" customWidth="1"/>
+    <col min="2" max="2" width="21" style="2" customWidth="1"/>
+    <col min="3" max="4" width="14" style="2" customWidth="1"/>
+    <col min="5" max="5" width="21" style="2" customWidth="1"/>
+    <col min="6" max="6" width="27" style="2" customWidth="1"/>
+    <col min="7" max="7" width="17" style="2" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="16384" width="17" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
-        <is>
-          <t>대사 ID</t>
-        </is>
-      </c>
-      <c r="B1" s="21" t="inlineStr">
-        <is>
-          <t>화자 이름 또는 캐릭터 ID</t>
-        </is>
-      </c>
-      <c r="C1" s="21" t="inlineStr">
-        <is>
-          <t>대사 내용</t>
-        </is>
-      </c>
-      <c r="D1" s="21" t="inlineStr">
-        <is>
-          <t>다음 대사 ID</t>
-        </is>
-      </c>
-      <c r="E1" s="21" t="inlineStr">
-        <is>
-          <t>선택지 이름 목록(| 구분)</t>
-        </is>
-      </c>
-      <c r="F1" s="22" t="inlineStr">
-        <is>
-          <t>선택지 이동 대사 ID 목록(| 구분)</t>
-        </is>
-      </c>
-      <c r="G1" s="22" t="inlineStr">
-        <is>
-          <t>캐릭터 일러스트 경로</t>
-        </is>
-      </c>
-      <c r="H1" s="22" t="inlineStr">
-        <is>
-          <t>음성 파일 경로</t>
-        </is>
+    <row r="1" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="2" ht="13" customHeight="1">
-      <c r="A2" s="23" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="B2" s="23" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C2" s="23" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D2" s="23" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E2" s="23" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F2" s="23" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="G2" s="24" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="H2" s="24" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
+    <row r="2" spans="1:15" ht="13" customHeight="1">
+      <c r="A2" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="20" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="3" ht="15.75" customFormat="1" customHeight="1" s="13">
-      <c r="A3" s="25" t="inlineStr">
-        <is>
-          <t>Id</t>
-        </is>
-      </c>
-      <c r="B3" s="25" t="inlineStr">
-        <is>
-          <t>SpeakerName</t>
-        </is>
-      </c>
-      <c r="C3" s="25" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="D3" s="25" t="inlineStr">
-        <is>
-          <t>NextDialogueId</t>
-        </is>
-      </c>
-      <c r="E3" s="25" t="inlineStr">
-        <is>
-          <t>SelectionNameList</t>
-        </is>
-      </c>
-      <c r="F3" s="25" t="inlineStr">
-        <is>
-          <t>SelectionDialogueIdList</t>
-        </is>
-      </c>
-      <c r="G3" s="26" t="inlineStr">
-        <is>
-          <t>TexturePath</t>
-        </is>
-      </c>
-      <c r="H3" s="26" t="inlineStr">
-        <is>
-          <t>VoicePath</t>
-        </is>
+    <row r="3" spans="1:15" s="11" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A3" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="22" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>character_Moran_01</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>모란</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>"치.직... 시.스.템. 가.동. 아.버.지! 저. 말.도. 하.고. 움.직.여.요. 가.슴.속. 태.엽.이. 진짜. 심.장. 처.럼. 쿵.쾅.거.립.니.다. 소.녀. 다.시. 인.사. 올.려.드.리.옵.니.다."</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="16" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="n"/>
-      <c r="L4" s="5" t="n"/>
-      <c r="M4" s="5" t="n"/>
-      <c r="N4" s="5" t="n"/>
-      <c r="O4" s="5" t="n"/>
+    <row r="4" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>character_JangYoungSim_01</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>장영심</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>“……장, 장금아……! 네가 정녕 돌아온 것이냐……!”</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
+    <row r="5" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>character_Mr.Jaeik_01</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>재익군</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>"끄응…! 어이쿠, 이 맛은 당최 무엇이구멍유?! 가슴 깊은 곳에서 뜨거운 기운이 확 솟구치는구멍! ……어라? 내, 내가 왜 두 발로 서 있는 거래유? 게다가 사람 말이 입 밖으로 막 나오잖습지멍?! 아이고 대감 천지신명이시여, 이게 무슨 기적이란 말이멍유!"</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
+    <row r="6" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>character_Chunyang_01</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>춘양</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>“재익아! 네 이놈, 어디 갔나 했더니 여기서 뭘 먹고…… 아니, 네가 어찌 사람의 옷을 입고 두 발로 서 있는 게냐? 귀신이 곡할 노릇이로구나!”</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
+    <row r="7" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>character_Mr.Jaeik_02</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>재익군</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>“아씨! 글쎄 이 신비로운 요리를 한 입 먹었더니만, 온몸의 털이 곤두서며 진짜로 말하는 사람이 되었구멍요!”</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
+    <row r="8" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>character_Moran_02</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>모란</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>“안녕하세요, 여러분! 음식으로 세상을 치유하는 멋진 여정을 떠나보려고 해요. 제 동료가 되어서 이 모험을 함께해 주시지 않겠어요?”</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
+    <row r="9" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A9" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>character_Chunyang_02</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>춘양</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>“나는 홀연히 자취를 감춘 서방님, 몽령 나으리를 찾기 위해 온 팔도를 헤매는 중이라오. 갈 길이 멀고 험난한 여정이 되겠으나…… 그대들의 이 신비로운 음식을 여정 내내 맛볼 수만 있다면, 내 기꺼이 길잡이가 되어 드리겠소.”</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
+    <row r="10" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>character_Chunyang_03</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>춘양</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>“우리 아버님께서 내어주신 참으로 귀한 쌀이라오. 자네들의 여정에 조금이나마 보탬이 되었으면 좋겠소.”</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="n"/>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
+    <row r="11" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>character_Moran_03</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>모란</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>“우리 집 마당에서 기른 귀한 채소들이에요. 참 맛좋은 음식들이 가득했었는데… 아쉽게도 다른 음식은 재익 군이 남김없이 다 먹어버렸지요! 하하.”</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="n"/>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
+    <row r="12" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>character_Mr.Jaeik_03</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>재익군</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>“아이고, 모란님… 면목이 없구멍유. 그 참을 수 없는 냄새에 저도 모르게 개 버릇을 못 고치고 주둥이가 먼저 나가버렸지 멍유……. 정말 미안하구멍유…….”</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="n"/>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="5" t="n"/>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
+    <row r="13" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>character_Chunyang_04</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>춘양</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>“모란님, 이 미련한 놈의 허물은 내 대신 사죄하겠소. 밥값을 하려면 부지런히 길을 나서야 할 터…… 먼저는 동쪽으로 가시지요. 그곳에 탐관오리의 수탈로 배 굶주린 자들이 유독 많다 들었습니다.”</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="5" t="n"/>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
+    <row r="14" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A14" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>character_Mr.Jaeik_04</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>재익군</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>“슬슬 날이 저무니 배가 고프지 않습니까요, 아씨? 제가 배고파서 그런 건 절대 아니구멍유……! 모란 님이 우리를 위해 맛난 요리를 해주신다면 참말로 감사하겠서요!”
-(그의 꼬리를 흔들리는걸 멈추지 않는 탓일가)</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
+    <row r="15" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>character_Chunyang_05</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>춘양</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>“그러고 보니 벌써 저녁때가 되었구려. 마침 다들 지쳤을 터인데, 낭자에게 염치 불고하고 따뜻한 식사를 부탁드려도 되겠소?”</t>
-        </is>
+    <row r="16" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A16" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>46</v>
       </c>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>character_Moran_04</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>모란</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>“당연히 해드려야죠! 가마솥을 뜨겁게 달굴 테니, 두 분 다 조금만 기다려주세요. 세상에서 가장 배부른 요리를 지어드릴게요!”</t>
-        </is>
+    <row r="17" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A17" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>character_Moran_05</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>모란</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>“따끈따끈한 ‘야채죽’이 완성되었어요! 소박하지만 지친 몸을 따뜻하게 데워줄 거예요. 어서 맛있게 드세요!”</t>
-        </is>
+    <row r="18" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A18" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>49</v>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="9" t="n"/>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
+    <row r="19" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A19" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="9" t="n"/>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="9" t="n"/>
+    <row r="20" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A20" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>55</v>
+      </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="9" t="n"/>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
+    <row r="21" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="9" t="n"/>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
+    <row r="22" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="9" t="n"/>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
+    <row r="23" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="9" t="n"/>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="9" t="n"/>
+    <row r="24" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="9" t="n"/>
-      <c r="B25" s="9" t="n"/>
-      <c r="C25" s="9" t="n"/>
-      <c r="E25" s="5" t="n"/>
+    <row r="25" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="E25" s="4"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="10" t="n"/>
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="10" t="n"/>
-      <c r="E26" s="5" t="n"/>
+    <row r="26" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="E26" s="4"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="10" t="n"/>
-      <c r="B27" s="10" t="n"/>
-      <c r="C27" s="10" t="n"/>
-      <c r="E27" s="5" t="n"/>
+    <row r="27" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="E27" s="4"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="10" t="n"/>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="n"/>
-      <c r="E28" s="5" t="n"/>
+    <row r="28" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="E28" s="4"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="10" t="n"/>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="10" t="n"/>
+    <row r="29" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="10" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
+    <row r="30" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="10" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
+    <row r="31" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="11" t="n"/>
-      <c r="B32" s="11" t="n"/>
-      <c r="C32" s="11" t="n"/>
+    <row r="32" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="11" t="n"/>
-      <c r="B33" s="11" t="n"/>
-      <c r="C33" s="11" t="n"/>
+    <row r="33" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="11" t="n"/>
-      <c r="B34" s="11" t="n"/>
-      <c r="C34" s="11" t="n"/>
+    <row r="34" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A34" s="10"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="11" t="n"/>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="11" t="n"/>
+    <row r="35" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A35" s="10"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1"/>
-    <row r="37" ht="15.75" customHeight="1"/>
-    <row r="38" ht="15.75" customHeight="1"/>
-    <row r="39" ht="15.75" customHeight="1"/>
-    <row r="40" ht="15.75" customHeight="1"/>
-    <row r="41" ht="15.75" customHeight="1"/>
-    <row r="42" ht="15.75" customHeight="1"/>
-    <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1"/>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="36" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="37" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="38" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="39" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="40" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="41" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="42" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="43" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="44" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="45" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="46" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="47" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="48" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
@@ -2142,7 +3474,8 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/OO_Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Dialogue.xlsx
@@ -1002,583 +1002,583 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <r>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>허어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>눈물이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>앞을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가리는구려</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">…… </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>은혜를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어찌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>갚아야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>할지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모르겠소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지금은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>척박해진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>땅이나</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>매서운</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>추위도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잊게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>만드는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>우리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마을의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오랜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>특산물인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>청양고추라오</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모란님의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>앞날에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>작게나마</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보탬이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>되길</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바라오</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.”</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>character_VillageChief_02</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>“</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>허어</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>눈물이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>앞을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>가리는구려</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">…… </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>은혜를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>어찌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>갚아야</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>할지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>모르겠소</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>비록</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>지금은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>척박해진</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>땅이나</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>매서운</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>추위도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>잊게</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>만드는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>우리</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>마을의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>오랜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>특산물인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>청양고추라오</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>모란님의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>앞날에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>작게나마</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>보탬이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>되길</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>바라오</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.”</t>
-    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -2420,13 +2420,13 @@
     </row>
     <row r="20" spans="1:5" ht="15.75" customHeight="1">
       <c r="A20" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>53</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15.75" customHeight="1">
@@ -3476,6 +3476,6 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/OO_Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Dialogue.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="99">
   <si>
     <t>대사 ID</t>
   </si>
@@ -127,13 +127,7 @@
     <t>“우리 아버님께서 내어주신 참으로 귀한 쌀이라오. 자네들의 여정에 조금이나마 보탬이 되었으면 좋겠소.”</t>
   </si>
   <si>
-    <t>character_Moran_03</t>
-  </si>
-  <si>
     <t>“우리 집 마당에서 기른 귀한 채소들이에요. 참 맛좋은 음식들이 가득했었는데… 아쉽게도 다른 음식은 재익 군이 남김없이 다 먹어버렸지요! 하하.”</t>
-  </si>
-  <si>
-    <t>character_Mr.Jaeik_03</t>
   </si>
   <si>
     <t>“아이고, 모란님… 면목이 없구멍유. 그 참을 수 없는 냄새에 저도 모르게 개 버릇을 못 고치고 주둥이가 먼저 나가버렸지 멍유……. 정말 미안하구멍유…….”</t>
@@ -152,19 +146,1461 @@
 (그의 꼬리를 흔들리는걸 멈추지 않는 탓일가)</t>
   </si>
   <si>
+    <t>“그러고 보니 벌써 저녁때가 되었구려. 마침 다들 지쳤을 터인데, 낭자에게 염치 불고하고 따뜻한 식사를 부탁드려도 되겠소?”</t>
+  </si>
+  <si>
+    <t>character_Moran_04</t>
+  </si>
+  <si>
+    <t>“당연히 해드려야죠! 가마솥을 뜨겁게 달굴 테니, 두 분 다 조금만 기다려주세요. 세상에서 가장 배부른 요리를 지어드릴게요!”</t>
+  </si>
+  <si>
+    <t>“따끈따끈한 ‘야채죽’이 완성되었어요! 소박하지만 지친 몸을 따뜻하게 데워줄 거예요. 어서 맛있게 드세요!”</t>
+  </si>
+  <si>
+    <r>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>포학한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>왕이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보낸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>탐관오리들이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가호마다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뼛속까지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수탈해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가니</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>우리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마을엔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>들쥐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>새끼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>먹을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>것조차</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>남지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않았소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>백성들이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>길가에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>쓰러져</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>굶어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>죽어가는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실정이오</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">……. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부디</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오늘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>단</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하루만이라도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지친</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이들의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주린</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>배를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>달래줄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>따뜻한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>온기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그릇을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나누어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>줄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없겠소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>?”</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_VillageChief_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>촌장</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>허어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>눈물이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>앞을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가리는구려</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">…… </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>은혜를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어찌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>갚아야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>할지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모르겠소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지금은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>척박해진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>땅이나</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>매서운</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>추위도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잊게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>만드는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>우리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마을의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오랜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>특산물인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>청양고추라오</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모란님의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>앞날에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>작게나마</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보탬이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>되길</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바라오</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.”</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_VillageChief_02</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>character_Chunyang_05</t>
-  </si>
-  <si>
-    <t>“그러고 보니 벌써 저녁때가 되었구려. 마침 다들 지쳤을 터인데, 낭자에게 염치 불고하고 따뜻한 식사를 부탁드려도 되겠소?”</t>
-  </si>
-  <si>
-    <t>character_Moran_04</t>
-  </si>
-  <si>
-    <t>“당연히 해드려야죠! 가마솥을 뜨겁게 달굴 테니, 두 분 다 조금만 기다려주세요. 세상에서 가장 배부른 요리를 지어드릴게요!”</t>
-  </si>
-  <si>
-    <t>“따끈따끈한 ‘야채죽’이 완성되었어요! 소박하지만 지친 몸을 따뜻하게 데워줄 거예요. 어서 맛있게 드세요!”</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>춘양</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Moran_03</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Chunyang_06</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -178,140 +1614,140 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>포학한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>왕이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>보낸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>탐관오리들이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>가호마다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>뼛속까지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수탈해</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>가니</t>
+      <t>이런</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>횡포를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부린</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>탐관오리에게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가셔서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>담판을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내시죠</t>
     </r>
     <r>
       <rPr>
@@ -330,662 +1766,624 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>이제</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>우리</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>마을엔</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>들쥐</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>새끼</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>마리</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>먹을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>것조차</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>남지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>않았소</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>백성들이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>길가에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>쓰러져</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>굶어</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>죽어가는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>실정이오</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">……. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>부디</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>오늘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>단</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>하루만이라도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>지친</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이들의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>주린</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>배를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>달래줄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>따뜻한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>온기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>그릇을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>나누어</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>줄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>없겠소</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>?”</t>
+      <t>모란님</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.”</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Mr.Jaeik_03</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Mr.Jaeik_05</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>재익군</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아씨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">~! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>탐관오리란</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>얼마나</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>무서운</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자인디</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>굳이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>거길</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가시려</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하십니까유</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">? </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지금은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>저희를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지켜줄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이몽령</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>도련님도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>안</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>계신단</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마류</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>~!”</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>춘양</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>“네 이놈! 감히 그 주둥이에 내 서방님의 이름을 함부로 올리지 마라!”</t>
+  </si>
+  <si>
+    <t>character_Mr.Jaeik_06</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>재익군</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이익</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">!!! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>죄송하구멍유</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>! (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>깜짝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>놀라</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>읍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>앞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>발이였던</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>손으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>입을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>틀어막는다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)”</t>
     </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -994,11 +2392,11 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>character_VillageChief_01</t>
+    <t>character_Moran_06</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>촌장</t>
+    <t>모란</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -1013,7 +2411,26 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>허어</t>
+      <t>춘양</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아씨</t>
     </r>
     <r>
       <rPr>
@@ -1032,45 +2449,3331 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>눈물이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>앞을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>가리는구려</t>
+      <t>너무</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>쓰지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마세요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>도련님을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>향한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아씨의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>깊은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마음을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>재익이가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미처</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>몰라보고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말실수를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모양입니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>재익군</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>무서운</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>건</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>당연하지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>우리가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>힘을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>합치면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>괜찮을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>거야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>촌장님이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주신</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>청양고추도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있으니</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기운</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수레를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>움직여볼까</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>?”</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>네</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이놈들</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감히</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수청을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>들지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>도망친</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>춘양을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>숨겨준</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>것도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모자라</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>요상한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수레로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>천한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>백성들을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>선동하며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>호박들을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>훔쳐가다니</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>당장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>저</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>고약한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>역적</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>놈들을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>포박하라</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>!”</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>이몽령</t>
+  </si>
+  <si>
+    <t xml:space="preserve">모란 </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>예</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>도련님</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마침</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>촌장님께</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>얻은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>귀한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>청양고추가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있으니</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아주</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>매콤한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>찌개를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>끓여</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대접하겠습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.”</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>탐관오리</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_GreedyDuck_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_GreedyDuck_02</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>저건</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>또</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어디서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>굴러먹다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>온</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>거렁뱅이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>놈이냐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감히</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>귀한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>곳에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>함부로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>발을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>디디다니</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>여봐라</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>저</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>고얀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>놈까지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>당장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>포승줄로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>꽁꽁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>묶어라</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>저</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>발칙한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>역적</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>패당</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>네</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>놈과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>함께</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>볼기를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>곤장으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>매우</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>쳐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>……!"</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_LeeMongRyong_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_LeeMongRyong_02</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>암행어사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>출두야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">—! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>백성들의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>고혈을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>짜내어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자신의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>배만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>불리던</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>탐관오리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>놈아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>네</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>죄를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>네가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>알렷다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>!"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t/>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모란아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>네</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>소문은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>익히</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>들었다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>벌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>위한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>음식을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>만들어보려구나</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.”</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Moran_07</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_GreedyDuck_03</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>탐관오리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>탐관오리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>: "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아이고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>죽네</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>입안에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>화룡이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>불을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뿜는구나</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">!! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>물</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>당장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>물을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가져오너라어어억</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>—!!"</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_LeeMongRyong_03</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>이몽령</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>떠내려가는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>탐관오리를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>헛기침을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하다가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>춘향을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>돌아보며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>) "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>덕분에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>큰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>소동</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>의로운</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마쳤소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. ……</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>춘양아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그동안</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>무탈하였느냐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오느라</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너무</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>늦었다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>고생이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>많았구나</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>."</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Chunyang_07</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Chunyang_08</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>춘양</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나으리</t>
     </r>
     <r>
       <rPr>
@@ -1089,6 +5792,82 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
+      <t>밤낮으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오직</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>서방님만을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그리워하며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
       <t>이</t>
     </r>
     <r>
@@ -1108,24 +5887,917 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>은혜를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
+      <t>모진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시간을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>버텨왔나이다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>."</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">character_LeeMongRyong_04 </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>"(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>춘양을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>따뜻하게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바라보며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>참으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마음이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비단결</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>동료들과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>함께하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있구나</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>."</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이곳에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>남아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>흩어진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>민심을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바로잡고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>왕실의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어둠을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>살필</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>테니</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>춘양</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자네는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>저들과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>함께</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>고통받는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>세상을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아름다운</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>여정을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>계속</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이어가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주시게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>."</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_LeeMongRyong_05</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>"(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>흐르는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>눈물을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>닦고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>입을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>가리며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>수줍게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>미소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>짓는다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>나으리의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>깊은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>뜻을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
       </rPr>
       <t>어찌</t>
     </r>
@@ -1134,83 +6806,27 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>갚아야</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>할지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>모르겠소</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>거스르겠나이다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">. </t>
     </r>
@@ -1218,75 +6834,159 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>비록</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>지금은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>척박해진</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>땅이나</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>서방님께서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>주신</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>영약과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>비단결</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>동료들이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>있으니</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">, </t>
     </r>
@@ -1294,170 +6994,99 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>매서운</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>추위도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>잊게</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>만드는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>우리</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>마을의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>오랜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>특산물인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>청양고추라오</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>앞길에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>두려울</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>것이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>없사옵니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">. </t>
     </r>
@@ -1465,120 +7094,258 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>모란님의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>앞날에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>작게나마</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>보탬이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>되길</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>바라오</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.”</t>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>부디</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>몸조심하시옵소서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>모험의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>끝에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>더</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>밝아진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>세상에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>반드시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>다시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>만나기를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>기약하겠나이다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>."</t>
     </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>character_VillageChief_02</t>
+    <r>
+      <t>character_Chunyang_0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>9</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1586,7 +7353,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1645,6 +7412,14 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1742,7 +7517,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1790,6 +7565,10 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2282,13 +8061,13 @@
     </row>
     <row r="12" spans="1:15" ht="15.75" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -2305,13 +8084,13 @@
     </row>
     <row r="13" spans="1:15" ht="15.75" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -2328,13 +8107,13 @@
     </row>
     <row r="14" spans="1:15" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -2351,13 +8130,13 @@
     </row>
     <row r="15" spans="1:15" ht="15.75" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -2374,141 +8153,242 @@
     </row>
     <row r="16" spans="1:15" ht="15.75" customHeight="1">
       <c r="A16" s="7" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B16" s="16" t="s">
         <v>27</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1">
       <c r="A17" s="8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>18</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15.75" customHeight="1">
       <c r="A18" s="8" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="B18" s="15" t="s">
         <v>18</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15.75" customHeight="1">
       <c r="A19" s="8" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
     </row>
     <row r="20" spans="1:5" ht="15.75" customHeight="1">
       <c r="A20" s="8" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
+      <c r="A21" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="22" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
+      <c r="A22" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="23" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
+      <c r="A23" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="24" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
+      <c r="A24" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="25" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
+      <c r="A25" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>69</v>
+      </c>
       <c r="E25" s="4"/>
     </row>
     <row r="26" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
+      <c r="A26" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>70</v>
+      </c>
       <c r="E26" s="4"/>
     </row>
     <row r="27" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
+      <c r="A27" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="E27" s="4"/>
     </row>
     <row r="28" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
+      <c r="A28" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B28" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>80</v>
+      </c>
       <c r="E28" s="4"/>
     </row>
     <row r="29" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
+      <c r="A29" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="E29" s="4"/>
     </row>
     <row r="30" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
+      <c r="A30" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B30" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="31" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
+      <c r="A31" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="32" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A32" s="10"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
+      <c r="A32" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B32" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
+      <c r="A33" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B33" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="34" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A34" s="10"/>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
+      <c r="A34" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B34" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="35" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
+      <c r="A35" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B35" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>95</v>
+      </c>
     </row>
-    <row r="36" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="36" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A36" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="B36" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="C36" s="26" t="s">
+        <v>97</v>
+      </c>
+    </row>
     <row r="37" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="38" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="39" spans="1:3" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/OO_Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Dialogue.xlsx
@@ -5943,626 +5943,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>"(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>춘양을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>따뜻하게</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>바라보며</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>참으로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>마음이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>비단결</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>같은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>동료들과</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>함께하고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있구나</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>."</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>나는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이곳에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>남아</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>흩어진</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>민심을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>바로잡고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>왕실의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>어둠을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>살필</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>테니</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>춘양</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>자네는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>저들과</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>함께</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>고통받는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>세상을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>구하는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>아름다운</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>여정을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>계속</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이어가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>주시게</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>."</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>character_LeeMongRyong_05</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -6586,6 +5966,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -6606,6 +5987,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -6626,6 +6008,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -6646,6 +6029,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -6666,6 +6050,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -6686,6 +6071,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -6706,6 +6092,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -6726,6 +6113,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">) </t>
@@ -6746,6 +6134,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -6766,6 +6155,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -6786,6 +6176,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -6806,6 +6197,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -6826,6 +6218,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">. </t>
@@ -6846,6 +6239,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -6866,6 +6260,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -6886,6 +6281,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -6906,6 +6302,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -6926,6 +6323,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -6946,6 +6344,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -6966,6 +6365,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -6986,6 +6386,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">, </t>
@@ -7006,6 +6407,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -7026,6 +6428,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -7046,6 +6449,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -7066,6 +6470,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -7086,6 +6491,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">. </t>
@@ -7106,6 +6512,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -7126,6 +6533,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">. </t>
@@ -7146,6 +6554,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -7166,6 +6575,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -7186,6 +6596,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">, </t>
@@ -7206,6 +6617,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -7226,6 +6638,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -7246,6 +6659,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -7266,6 +6680,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -7286,6 +6701,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -7306,6 +6722,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -7326,6 +6743,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>."</t>
@@ -7345,6 +6763,920 @@
         <scheme val="minor"/>
       </rPr>
       <t>9</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>"(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>춘양을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>따뜻하게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바라보며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>) "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>참으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비단결</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마음을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>동료들과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>함께하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있구나</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이곳에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>남아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>흩어진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>민심을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바로잡고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>왕실의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어둠을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>살필</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>테니</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>춘양</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자네는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>저들과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>함께</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>고통받는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>세상을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아름다운</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>여정을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>계속</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이어가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주시게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너희의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>여정에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보탬이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>되길</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바라며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>쌀과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>꿀단지를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내어주니</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부디</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>요긴하게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>쓰이길</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바란다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>."</t>
     </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -8364,29 +8696,29 @@
         <v>87</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15.75" customHeight="1">
       <c r="A35" s="10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B35" s="24" t="s">
         <v>87</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15.75" customHeight="1">
       <c r="A36" s="26" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B36" s="25" t="s">
         <v>91</v>
       </c>
       <c r="C36" s="26" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/OO_Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Dialogue.xlsx
@@ -1,101 +1,426 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="12770" yWindow="2240" windowWidth="19820" windowHeight="18420" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="12770" yWindow="2240" windowWidth="19820" windowHeight="18420"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DNTable_Dialogue" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="DNTable_Dialogue" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="105">
+  <si>
+    <t>대사 ID</t>
+  </si>
+  <si>
+    <t>화자 이름 또는 캐릭터 ID</t>
+  </si>
+  <si>
+    <t>대사 내용</t>
+  </si>
+  <si>
+    <t>다음 대사 ID</t>
+  </si>
+  <si>
+    <t>선택지 이름 목록(| 구분)</t>
+  </si>
+  <si>
+    <t>선택지 이동 대사 ID 목록(| 구분)</t>
+  </si>
+  <si>
+    <t>캐릭터 일러스트 경로</t>
+  </si>
+  <si>
+    <t>음성 파일 경로</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>SpeakerName</t>
+  </si>
+  <si>
+    <t>Text</t>
+  </si>
+  <si>
+    <t>NextDialogueId</t>
+  </si>
+  <si>
+    <t>SelectionNameList</t>
+  </si>
+  <si>
+    <t>SelectionDialogueIdList</t>
+  </si>
+  <si>
+    <t>TexturePath</t>
+  </si>
+  <si>
+    <t>VoicePath</t>
+  </si>
+  <si>
+    <t>character_Moran_01</t>
+  </si>
+  <si>
+    <t>모란</t>
+  </si>
+  <si>
+    <t>"치.직... 시.스.템. 가.동. 아.버.지! 저. 말.도. 하.고. 움.직.여.요. 가.슴.속. 태.엽.이. 진짜. 심.장. 처.럼. 쿵.쾅.거.립.니.다. 소.녀. 다.시. 인.사. 올.려.드.리.옵.니.다."</t>
+  </si>
+  <si>
+    <t>character_JangYoungSim_01</t>
+  </si>
+  <si>
+    <t>장영심</t>
+  </si>
+  <si>
+    <t>“……장, 장금아……! 네가 정녕 돌아온 것이냐……!”</t>
+  </si>
+  <si>
+    <t>character_Mr.Jaeik_01</t>
+  </si>
+  <si>
+    <t>재익군</t>
+  </si>
+  <si>
+    <t>"끄응…! 어이쿠, 이 맛은 당최 무엇이구멍유?! 가슴 깊은 곳에서 뜨거운 기운이 확 솟구치는구멍! ……어라? 내, 내가 왜 두 발로 서 있는 거래유? 게다가 사람 말이 입 밖으로 막 나오잖습지멍?! 아이고 대감 천지신명이시여, 이게 무슨 기적이란 말이멍유!"</t>
+  </si>
+  <si>
+    <t>character_Chunyang_01</t>
+  </si>
+  <si>
+    <t>춘양</t>
+  </si>
+  <si>
+    <t>“재익아! 네 이놈, 어디 갔나 했더니 여기서 뭘 먹고…… 아니, 네가 어찌 사람의 옷을 입고 두 발로 서 있는 게냐? 귀신이 곡할 노릇이로구나!”</t>
+  </si>
+  <si>
+    <t>character_Mr.Jaeik_02</t>
+  </si>
+  <si>
+    <t>“아씨! 글쎄 이 신비로운 요리를 한 입 먹었더니만, 온몸의 털이 곤두서며 진짜로 말하는 사람이 되었구멍요!”</t>
+  </si>
+  <si>
+    <t>character_Moran_02</t>
+  </si>
+  <si>
+    <t>“안녕하세요, 여러분! 음식으로 세상을 치유하는 멋진 여정을 떠나보려고 해요. 제 동료가 되어서 이 모험을 함께해 주시지 않겠어요?”</t>
+  </si>
+  <si>
+    <t>character_Chunyang_02</t>
+  </si>
+  <si>
+    <t>“나는 홀연히 자취를 감춘 서방님, 몽령 나으리를 찾기 위해 온 팔도를 헤매는 중이라오. 갈 길이 멀고 험난한 여정이 되겠으나…… 그대들의 이 신비로운 음식을 여정 내내 맛볼 수만 있다면, 내 기꺼이 길잡이가 되어 드리겠소.”</t>
+  </si>
+  <si>
+    <t>character_Chunyang_03</t>
+  </si>
+  <si>
+    <t>“우리 아버님께서 내어주신 참으로 귀한 쌀이라오. 자네들의 여정에 조금이나마 보탬이 되었으면 좋겠소.”</t>
+  </si>
+  <si>
+    <t>character_Moran_03</t>
+  </si>
+  <si>
+    <t>“우리 집 마당에서 기른 귀한 채소들이에요. 참 맛좋은 음식들이 가득했었는데… 아쉽게도 다른 음식은 재익 군이 남김없이 다 먹어버렸지요! 하하.”</t>
+  </si>
+  <si>
+    <t>character_Mr.Jaeik_03</t>
+  </si>
+  <si>
+    <t>“아이고, 모란님… 면목이 없구멍유. 그 참을 수 없는 냄새에 저도 모르게 개 버릇을 못 고치고 주둥이가 먼저 나가버렸지 멍유……. 정말 미안하구멍유…….”</t>
+  </si>
+  <si>
+    <t>character_Chunyang_04</t>
+  </si>
+  <si>
+    <t>“모란님, 이 미련한 놈의 허물은 내 대신 사죄하겠소. 밥값을 하려면 부지런히 길을 나서야 할 터…… 먼저는 동쪽으로 가시지요. 그곳에 탐관오리의 수탈로 배 굶주린 자들이 유독 많다 들었습니다.”</t>
+  </si>
+  <si>
+    <t>character_Mr.Jaeik_04</t>
+  </si>
+  <si>
+    <t>“슬슬 날이 저무니 배가 고프지 않습니까요, 아씨? 제가 배고파서 그런 건 절대 아니구멍유……! 모란 님이 우리를 위해 맛난 요리를 해주신다면 참말로 감사하겠서요!”
+(그의 꼬리를 흔들리는걸 멈추지 않는 탓일가)</t>
+  </si>
+  <si>
+    <t>character_Chunyang_05</t>
+  </si>
+  <si>
+    <t>“그러고 보니 벌써 저녁때가 되었구려. 마침 다들 지쳤을 터인데, 낭자에게 염치 불고하고 따뜻한 식사를 부탁드려도 되겠소?”</t>
+  </si>
+  <si>
+    <t>character_Moran_04</t>
+  </si>
+  <si>
+    <t>“당연히 해드려야죠! 가마솥을 뜨겁게 달굴 테니, 두 분 다 조금만 기다려주세요. 세상에서 가장 배부른 요리를 지어드릴게요!”</t>
+  </si>
+  <si>
+    <t>character_Moran_05</t>
+  </si>
+  <si>
+    <t>“따끈따끈한 ‘야채죽’이 완성되었어요! 소박하지만 지친 몸을 따뜻하게 데워줄 거예요. 어서 맛있게 드세요!”</t>
+  </si>
+  <si>
+    <t>character_VillageChief_01</t>
+  </si>
+  <si>
+    <t>촌장</t>
+  </si>
+  <si>
+    <t>“포학한 왕이 보낸 탐관오리들이 가호마다 뼛속까지 수탈해 가니, 이제 우리 마을엔 들쥐 새끼 한 마리 먹을 것조차 남지 않았소. 백성들이 길가에 쓰러져 굶어 죽어가는 실정이오……. 부디, 오늘 단 하루만이라도 이 지친 이들의 주린 배를 달래줄 따뜻한 온기 한 그릇을 나누어 줄 수 없겠소?”</t>
+  </si>
+  <si>
+    <t>character_VillageChief_02</t>
+  </si>
+  <si>
+    <t>“허어, 눈물이 앞을 가리는구려…… 이 은혜를 어찌 다 갚아야 할지 모르겠소. 비록 지금은 척박해진 땅이나, 매서운 추위도 잊게 만드는 우리 마을의 오랜 특산물인 청양고추라오. 모란님의 앞날에 작게나마 보탬이 되길 바라오.”</t>
+  </si>
+  <si>
+    <t>character_Chunyang_06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">춘양 </t>
+  </si>
+  <si>
+    <t>“이런 횡포를 부린 자인 탐관오리에게 가셔서 담판을 내시죠, 모란님.”</t>
+  </si>
+  <si>
+    <t>character_Mr.Jaeik_05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">재익군 </t>
+  </si>
+  <si>
+    <t>“아씨~! 탐관오리란 자가 얼마나 무서운 자인디 굳이 거길 가시려 하십니까유? 지금은 저희를 지켜줄 이몽령 도련님도 안 계신단 마류~!”</t>
+  </si>
+  <si>
+    <t>character_Chunyang_07</t>
+  </si>
+  <si>
+    <t>“네 이놈! 감히 그 주둥이에 내 서방님의 이름을 함부로 올리지 마라!”</t>
+  </si>
+  <si>
+    <t>character_Mr.Jaeik_06</t>
+  </si>
+  <si>
+    <t>“이익!!! 죄송하구멍유! (깜짝 놀라 읍! 하고 앞 발이였던 손으로 입을 틀어막는다)”</t>
+  </si>
+  <si>
+    <t>character_Moran_06</t>
+  </si>
+  <si>
+    <t>“춘양 아씨, 너무 마음 쓰지 마세요. 도련님을 향한 아씨의 깊은 마음을 재익이가 미처 몰라보고 말실수를 한 모양입니다. 재익군, 무서운 건 당연하지만 우리가 힘을 합치면 괜찮을 거야. 촌장님이 주신 청양고추도 있으니 기운 내서 수레를 움직여볼까?”</t>
+  </si>
+  <si>
+    <t>character_GreedyDuck_01</t>
+  </si>
+  <si>
+    <t>탐관오리</t>
+  </si>
+  <si>
+    <t>“네 이놈들! 감히 내 수청을 들지 않고 도망친 춘양을 숨겨준 것도 모자라, 요상한 수레로 천한 백성들을 선동하며 내 호박들을 훔쳐가다니! 당장 저 고약한 역적 놈들을 포박하라!”</t>
+  </si>
+  <si>
+    <t>character_GreedyDuck_02</t>
+  </si>
+  <si>
+    <t>"저건 또 어디서 굴러먹다 온 거렁뱅이 놈이냐! 감히 이 귀한 곳에 함부로 발을 디디다니! 여봐라, 저 고얀 놈까지 당장 포승줄로 꽁꽁 묶어라! 저 발칙한 역적 패당 네 놈과 함께 볼기를 곤장으로 매우 쳐……!"</t>
+  </si>
+  <si>
+    <t>character_LeeMongRyong_01</t>
+  </si>
+  <si>
+    <t>이몽령</t>
+  </si>
+  <si>
+    <t>“암행어사 출두야—! 백성들의 고혈을 짜내어 자신의 배만 불리던 탐관오리 놈아, 네 죄를 네가 알렷다!"</t>
+  </si>
+  <si>
+    <t>character_LeeMongRyong_02</t>
+  </si>
+  <si>
+    <t>"모란아, 네 소문은 익히 들었다. 이 자를 벌 하기 위한 음식을 만들어보려구나.”</t>
+  </si>
+  <si>
+    <t>character_Moran_07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">모란 </t>
+  </si>
+  <si>
+    <t>“예, 도련님. 마침 마을 촌장님께 얻은 귀한 청양고추가 있으니, 아주 매콤한 찌개를 끓여 대접하겠습니다.”</t>
+  </si>
+  <si>
+    <t>character_GreedyDuck_03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">탐관오리 </t>
+  </si>
+  <si>
+    <t>탐관오리: "아이고, 나 죽네! 입안에서 화룡이 불을 뿜는구나!! 물! 당장 물을 가져오너라어어억—!!"</t>
+  </si>
+  <si>
+    <t>character_LeeMongRyong_03</t>
+  </si>
+  <si>
+    <t>(떠내려가는 탐관오리를 보며 헛기침을 하다가, 이내 춘향을 돌아보며) "덕분에 큰 소동 없이 의로운 일을 마쳤소. ……춘양아, 그동안 무탈하였느냐. 내 오느라 너무 늦었다. 그간 고생이 많았구나."</t>
+  </si>
+  <si>
+    <t>character_Chunyang_08</t>
+  </si>
+  <si>
+    <t>"나으리…… 밤낮으로 오직 서방님만을 그리워하며 이 모진 시간을 버텨왔나이다."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">character_LeeMongRyong_04 </t>
+  </si>
+  <si>
+    <t>"(춘양을 따뜻하게 바라보며) "참으로 비단결 같은 마음을 가진 동료들과 함께하고 있구나."</t>
+  </si>
+  <si>
+    <t>character_LeeMongRyong_05</t>
+  </si>
+  <si>
+    <t>"나는 이곳에 남아 흩어진 민심을 바로잡고 왕실의 어둠을 살필 테니, 춘양 자네는 저들과 함께 고통받는 세상을 구하는 아름다운 여정을 계속 이어가 주시게. 내 너희의 여정에 보탬이 되길 바라며 이 쌀과 꿀단지를 내어주니, 부디 요긴하게 쓰이길 바란다."</t>
+  </si>
+  <si>
+    <t>character_Chunyang_09</t>
+  </si>
+  <si>
+    <t>"(흐르는 눈물을 닦고 입을 가리며 수줍게 미소 짓는다) 나으리의 깊은 뜻을 어찌 거스르겠나이다. 서방님께서 주신 영약과 이 비단결 같은 동료들이 있으니, 제 앞길에 두려울 것이 없사옵니다. 부디 몸조심하시옵소서. 이 모험의 끝에서, 더 밝아진 세상에서 반드시 다시 만나기를 기약하겠나이다."</t>
+  </si>
+  <si>
+    <t>산군</t>
+  </si>
+  <si>
+    <t>“웬 똥개 한 마리가 감히 내 앞길을 막아서고 짖는단 말이냐? 하하하! 하룻강아지 범 무서운 줄 모른다더니, 딱 너를 두고 하는 말이로구나!”</t>
+  </si>
+  <si>
+    <t>character_Moran_08</t>
+  </si>
+  <si>
+    <t>“먹을 것을 달라면 만들어 드릴 수 있습니다. 다만 사람을 해치는 일은 멈춰 주십시오.”</t>
+  </si>
+  <si>
+    <t>character_Sangun_03</t>
+  </si>
+  <si>
+    <t>“크흐흡…… 조그만 녀석이 제법 당차구나. 좋다! 어디 그 황금 꿀떡이라는 것을 당장 만들어 보거라. 만약 내 입에 맞지 않으면…… 알지?”</t>
+  </si>
+  <si>
+    <t>character_Sangun_04</t>
+  </si>
+  <si>
+    <t>“어흐응……! 내 평생 이토록 달콤하고 쫄깃한 떡은 처음이로구나. 사람을 해치며 날뛰던 가슴속 불길이 온데간데없이 가라앉는구나. 미안한 마음을 담아, 깊은 숲의 기운을 머금은 당근을 줄 터이니 받아 가거라.”</t>
+  </si>
+  <si>
+    <t>“어흥—! 떡 하나 주면 안 잡아먹지!”</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Sangun_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Sangun_02</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="12">
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="&quot;맑은 고딕&quot;"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="8"/>
       <name val="Arial"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <sz val="8"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="돋움"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <color theme="1"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="돋움"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-      <b val="1"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="?? ??"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="맑은 고딕"/>
-      <sz val="10"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="11">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -126,7 +451,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.7999816888943144"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -147,7 +472,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -193,146 +518,78 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="30">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -533,997 +790,716 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="17" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:O1000"/>
+  <sheetFormatPr defaultColWidth="17" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="14" customWidth="1" style="2" min="1" max="1"/>
-    <col width="21" customWidth="1" style="2" min="2" max="2"/>
-    <col width="14" customWidth="1" style="2" min="3" max="4"/>
-    <col width="21" customWidth="1" style="2" min="5" max="5"/>
-    <col width="27" customWidth="1" style="2" min="6" max="6"/>
-    <col width="17" customWidth="1" style="2" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" style="2" min="9" max="16384"/>
+    <col min="1" max="1" width="14" style="2" customWidth="1"/>
+    <col min="2" max="2" width="21" style="2" customWidth="1"/>
+    <col min="3" max="4" width="14" style="2" customWidth="1"/>
+    <col min="5" max="5" width="21" style="2" customWidth="1"/>
+    <col min="6" max="6" width="27" style="2" customWidth="1"/>
+    <col min="7" max="7" width="17" style="2" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="17" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="17" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="17" t="inlineStr">
-        <is>
-          <t>대사 ID</t>
-        </is>
-      </c>
-      <c r="B1" s="17" t="inlineStr">
-        <is>
-          <t>화자 이름 또는 캐릭터 ID</t>
-        </is>
-      </c>
-      <c r="C1" s="17" t="inlineStr">
-        <is>
-          <t>대사 내용</t>
-        </is>
-      </c>
-      <c r="D1" s="17" t="inlineStr">
-        <is>
-          <t>다음 대사 ID</t>
-        </is>
-      </c>
-      <c r="E1" s="17" t="inlineStr">
-        <is>
-          <t>선택지 이름 목록(| 구분)</t>
-        </is>
-      </c>
-      <c r="F1" s="18" t="inlineStr">
-        <is>
-          <t>선택지 이동 대사 ID 목록(| 구분)</t>
-        </is>
-      </c>
-      <c r="G1" s="18" t="inlineStr">
-        <is>
-          <t>캐릭터 일러스트 경로</t>
-        </is>
-      </c>
-      <c r="H1" s="18" t="inlineStr">
-        <is>
-          <t>음성 파일 경로</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="13" customHeight="1">
-      <c r="A2" s="19" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="B2" s="19" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C2" s="19" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D2" s="19" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E2" s="19" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F2" s="19" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="G2" s="20" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="H2" s="20" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customFormat="1" customHeight="1" s="11">
-      <c r="A3" s="21" t="inlineStr">
-        <is>
-          <t>Id</t>
-        </is>
-      </c>
-      <c r="B3" s="21" t="inlineStr">
-        <is>
-          <t>SpeakerName</t>
-        </is>
-      </c>
-      <c r="C3" s="21" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="D3" s="21" t="inlineStr">
-        <is>
-          <t>NextDialogueId</t>
-        </is>
-      </c>
-      <c r="E3" s="21" t="inlineStr">
-        <is>
-          <t>SelectionNameList</t>
-        </is>
-      </c>
-      <c r="F3" s="21" t="inlineStr">
-        <is>
-          <t>SelectionDialogueIdList</t>
-        </is>
-      </c>
-      <c r="G3" s="22" t="inlineStr">
-        <is>
-          <t>TexturePath</t>
-        </is>
-      </c>
-      <c r="H3" s="22" t="inlineStr">
-        <is>
-          <t>VoicePath</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>character_Moran_01</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>모란</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>"치.직... 시.스.템. 가.동. 아.버.지! 저. 말.도. 하.고. 움.직.여.요. 가.슴.속. 태.엽.이. 진짜. 심.장. 처.럼. 쿵.쾅.거.립.니.다. 소.녀. 다.시. 인.사. 올.려.드.리.옵.니.다."</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="12" t="n"/>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="n"/>
-      <c r="J4" s="4" t="n"/>
-      <c r="K4" s="4" t="n"/>
-      <c r="L4" s="4" t="n"/>
-      <c r="M4" s="4" t="n"/>
-      <c r="N4" s="4" t="n"/>
-      <c r="O4" s="4" t="n"/>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>character_JangYoungSim_01</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>장영심</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>“……장, 장금아……! 네가 정녕 돌아온 것이냐……!”</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-      <c r="L5" s="4" t="n"/>
-      <c r="M5" s="4" t="n"/>
-      <c r="N5" s="4" t="n"/>
-      <c r="O5" s="4" t="n"/>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>character_Mr.Jaeik_01</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>재익군</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>"끄응…! 어이쿠, 이 맛은 당최 무엇이구멍유?! 가슴 깊은 곳에서 뜨거운 기운이 확 솟구치는구멍! ……어라? 내, 내가 왜 두 발로 서 있는 거래유? 게다가 사람 말이 입 밖으로 막 나오잖습지멍?! 아이고 대감 천지신명이시여, 이게 무슨 기적이란 말이멍유!"</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="4" t="n"/>
-      <c r="J6" s="4" t="n"/>
-      <c r="K6" s="4" t="n"/>
-      <c r="L6" s="4" t="n"/>
-      <c r="M6" s="4" t="n"/>
-      <c r="N6" s="4" t="n"/>
-      <c r="O6" s="4" t="n"/>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>character_Chunyang_01</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>춘양</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>“재익아! 네 이놈, 어디 갔나 했더니 여기서 뭘 먹고…… 아니, 네가 어찌 사람의 옷을 입고 두 발로 서 있는 게냐? 귀신이 곡할 노릇이로구나!”</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
-      <c r="L7" s="4" t="n"/>
-      <c r="M7" s="4" t="n"/>
-      <c r="N7" s="4" t="n"/>
-      <c r="O7" s="4" t="n"/>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>character_Mr.Jaeik_02</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>재익군</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>“아씨! 글쎄 이 신비로운 요리를 한 입 먹었더니만, 온몸의 털이 곤두서며 진짜로 말하는 사람이 되었구멍요!”</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="4" t="n"/>
-      <c r="H8" s="4" t="n"/>
-      <c r="I8" s="4" t="n"/>
-      <c r="J8" s="4" t="n"/>
-      <c r="K8" s="4" t="n"/>
-      <c r="L8" s="4" t="n"/>
-      <c r="M8" s="4" t="n"/>
-      <c r="N8" s="4" t="n"/>
-      <c r="O8" s="4" t="n"/>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>character_Moran_02</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>모란</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>“안녕하세요, 여러분! 음식으로 세상을 치유하는 멋진 여정을 떠나보려고 해요. 제 동료가 되어서 이 모험을 함께해 주시지 않겠어요?”</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
-      <c r="L9" s="4" t="n"/>
-      <c r="M9" s="4" t="n"/>
-      <c r="N9" s="4" t="n"/>
-      <c r="O9" s="4" t="n"/>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>character_Chunyang_02</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>춘양</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>“나는 홀연히 자취를 감춘 서방님, 몽령 나으리를 찾기 위해 온 팔도를 헤매는 중이라오. 갈 길이 멀고 험난한 여정이 되겠으나…… 그대들의 이 신비로운 음식을 여정 내내 맛볼 수만 있다면, 내 기꺼이 길잡이가 되어 드리겠소.”</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="4" t="n"/>
-      <c r="I10" s="4" t="n"/>
-      <c r="J10" s="4" t="n"/>
-      <c r="K10" s="4" t="n"/>
-      <c r="L10" s="4" t="n"/>
-      <c r="M10" s="4" t="n"/>
-      <c r="N10" s="4" t="n"/>
-      <c r="O10" s="4" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>character_Chunyang_03</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>춘양</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>“우리 아버님께서 내어주신 참으로 귀한 쌀이라오. 자네들의 여정에 조금이나마 보탬이 되었으면 좋겠소.”</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="n"/>
-      <c r="K11" s="4" t="n"/>
-      <c r="L11" s="4" t="n"/>
-      <c r="M11" s="4" t="n"/>
-      <c r="N11" s="4" t="n"/>
-      <c r="O11" s="4" t="n"/>
-    </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>character_Moran_03</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>모란</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>“우리 집 마당에서 기른 귀한 채소들이에요. 참 맛좋은 음식들이 가득했었는데… 아쉽게도 다른 음식은 재익 군이 남김없이 다 먹어버렸지요! 하하.”</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n"/>
-      <c r="I12" s="4" t="n"/>
-      <c r="J12" s="4" t="n"/>
-      <c r="K12" s="4" t="n"/>
-      <c r="L12" s="4" t="n"/>
-      <c r="M12" s="4" t="n"/>
-      <c r="N12" s="4" t="n"/>
-      <c r="O12" s="4" t="n"/>
-    </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>character_Mr.Jaeik_03</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>재익군</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>“아이고, 모란님… 면목이 없구멍유. 그 참을 수 없는 냄새에 저도 모르게 개 버릇을 못 고치고 주둥이가 먼저 나가버렸지 멍유……. 정말 미안하구멍유…….”</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="4" t="n"/>
-      <c r="I13" s="4" t="n"/>
-      <c r="J13" s="4" t="n"/>
-      <c r="K13" s="4" t="n"/>
-      <c r="L13" s="4" t="n"/>
-      <c r="M13" s="4" t="n"/>
-      <c r="N13" s="4" t="n"/>
-      <c r="O13" s="4" t="n"/>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>character_Chunyang_04</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>춘양</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>“모란님, 이 미련한 놈의 허물은 내 대신 사죄하겠소. 밥값을 하려면 부지런히 길을 나서야 할 터…… 먼저는 동쪽으로 가시지요. 그곳에 탐관오리의 수탈로 배 굶주린 자들이 유독 많다 들었습니다.”</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n"/>
-      <c r="J14" s="4" t="n"/>
-      <c r="K14" s="4" t="n"/>
-      <c r="L14" s="4" t="n"/>
-      <c r="M14" s="4" t="n"/>
-      <c r="N14" s="4" t="n"/>
-      <c r="O14" s="4" t="n"/>
-    </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>character_Mr.Jaeik_04</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>재익군</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>“슬슬 날이 저무니 배가 고프지 않습니까요, 아씨? 제가 배고파서 그런 건 절대 아니구멍유……! 모란 님이 우리를 위해 맛난 요리를 해주신다면 참말로 감사하겠서요!”
-(그의 꼬리를 흔들리는걸 멈추지 않는 탓일가)</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="n"/>
-      <c r="J15" s="4" t="n"/>
-      <c r="K15" s="4" t="n"/>
-      <c r="L15" s="4" t="n"/>
-      <c r="M15" s="4" t="n"/>
-      <c r="N15" s="4" t="n"/>
-      <c r="O15" s="4" t="n"/>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>character_Chunyang_05</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>춘양</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>“그러고 보니 벌써 저녁때가 되었구려. 마침 다들 지쳤을 터인데, 낭자에게 염치 불고하고 따뜻한 식사를 부탁드려도 되겠소?”</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>character_Moran_04</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>모란</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>“당연히 해드려야죠! 가마솥을 뜨겁게 달굴 테니, 두 분 다 조금만 기다려주세요. 세상에서 가장 배부른 요리를 지어드릴게요!”</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>character_Moran_05</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>모란</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>“따끈따끈한 ‘야채죽’이 완성되었어요! 소박하지만 지친 몸을 따뜻하게 데워줄 거예요. 어서 맛있게 드세요!”</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>character_VillageChief_01</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>촌장</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>“포학한 왕이 보낸 탐관오리들이 가호마다 뼛속까지 수탈해 가니, 이제 우리 마을엔 들쥐 새끼 한 마리 먹을 것조차 남지 않았소. 백성들이 길가에 쓰러져 굶어 죽어가는 실정이오……. 부디, 오늘 단 하루만이라도 이 지친 이들의 주린 배를 달래줄 따뜻한 온기 한 그릇을 나누어 줄 수 없겠소?”</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>character_VillageChief_02</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>촌장</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>“허어, 눈물이 앞을 가리는구려…… 이 은혜를 어찌 다 갚아야 할지 모르겠소. 비록 지금은 척박해진 땅이나, 매서운 추위도 잊게 만드는 우리 마을의 오랜 특산물인 청양고추라오. 모란님의 앞날에 작게나마 보탬이 되길 바라오.”</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>character_Chunyang_06</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">춘양 </t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>“이런 횡포를 부린 자인 탐관오리에게 가셔서 담판을 내시죠, 모란님.”</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>character_Mr.Jaeik_05</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">재익군 </t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>“아씨~! 탐관오리란 자가 얼마나 무서운 자인디 굳이 거길 가시려 하십니까유? 지금은 저희를 지켜줄 이몽령 도련님도 안 계신단 마류~!”</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>character_Chunyang_07</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="inlineStr">
-        <is>
-          <t>춘양</t>
-        </is>
-      </c>
-      <c r="C23" s="13" t="inlineStr">
-        <is>
-          <t>“네 이놈! 감히 그 주둥이에 내 서방님의 이름을 함부로 올리지 마라!”</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>character_Mr.Jaeik_06</t>
-        </is>
-      </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>재익군</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>“이익!!! 죄송하구멍유! (깜짝 놀라 읍! 하고 앞 발이였던 손으로 입을 틀어막는다)”</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>character_Moran_06</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>모란</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>“춘양 아씨, 너무 마음 쓰지 마세요. 도련님을 향한 아씨의 깊은 마음을 재익이가 미처 몰라보고 말실수를 한 모양입니다. 재익군, 무서운 건 당연하지만 우리가 힘을 합치면 괜찮을 거야. 촌장님이 주신 청양고추도 있으니 기운 내서 수레를 움직여볼까?”</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="n"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>character_GreedyDuck_01</t>
-        </is>
-      </c>
-      <c r="B26" s="23" t="inlineStr">
-        <is>
-          <t>탐관오리</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>“네 이놈들! 감히 내 수청을 들지 않고 도망친 춘양을 숨겨준 것도 모자라, 요상한 수레로 천한 백성들을 선동하며 내 호박들을 훔쳐가다니! 당장 저 고약한 역적 놈들을 포박하라!”</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="n"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>character_GreedyDuck_02</t>
-        </is>
-      </c>
-      <c r="B27" s="23" t="inlineStr">
-        <is>
-          <t>탐관오리</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>"저건 또 어디서 굴러먹다 온 거렁뱅이 놈이냐! 감히 이 귀한 곳에 함부로 발을 디디다니! 여봐라, 저 고얀 놈까지 당장 포승줄로 꽁꽁 묶어라! 저 발칙한 역적 패당 네 놈과 함께 볼기를 곤장으로 매우 쳐……!"</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="n"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>character_LeeMongRyong_01</t>
-        </is>
-      </c>
-      <c r="B28" s="23" t="inlineStr">
-        <is>
-          <t>이몽령</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>“암행어사 출두야—! 백성들의 고혈을 짜내어 자신의 배만 불리던 탐관오리 놈아, 네 죄를 네가 알렷다!"</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="n"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>character_LeeMongRyong_02</t>
-        </is>
-      </c>
-      <c r="B29" s="23" t="inlineStr">
-        <is>
-          <t>이몽령</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>"모란아, 네 소문은 익히 들었다. 이 자를 벌 하기 위한 음식을 만들어보려구나.”</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="n"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>character_Moran_07</t>
-        </is>
-      </c>
-      <c r="B30" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">모란 </t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>“예, 도련님. 마침 마을 촌장님께 얻은 귀한 청양고추가 있으니, 아주 매콤한 찌개를 끓여 대접하겠습니다.”</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>character_GreedyDuck_03</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">탐관오리 </t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>탐관오리: "아이고, 나 죽네! 입안에서 화룡이 불을 뿜는구나!! 물! 당장 물을 가져오너라어어억—!!"</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>character_LeeMongRyong_03</t>
-        </is>
-      </c>
-      <c r="B32" s="24" t="inlineStr">
-        <is>
-          <t>이몽령</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>(떠내려가는 탐관오리를 보며 헛기침을 하다가, 이내 춘향을 돌아보며) "덕분에 큰 소동 없이 의로운 일을 마쳤소. ……춘양아, 그동안 무탈하였느냐. 내 오느라 너무 늦었다. 그간 고생이 많았구나."</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>character_Chunyang_08</t>
-        </is>
-      </c>
-      <c r="B33" s="24" t="inlineStr">
-        <is>
-          <t>춘양</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="inlineStr">
-        <is>
-          <t>"나으리…… 밤낮으로 오직 서방님만을 그리워하며 이 모진 시간을 버텨왔나이다."</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">character_LeeMongRyong_04 </t>
-        </is>
-      </c>
-      <c r="B34" s="24" t="inlineStr">
-        <is>
-          <t>이몽령</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>"(춘양을 따뜻하게 바라보며) "참으로 비단결 같은 마음을 가진 동료들과 함께하고 있구나."</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>character_LeeMongRyong_05</t>
-        </is>
-      </c>
-      <c r="B35" s="24" t="inlineStr">
-        <is>
-          <t>이몽령</t>
-        </is>
-      </c>
-      <c r="C35" s="10" t="inlineStr">
-        <is>
-          <t>"나는 이곳에 남아 흩어진 민심을 바로잡고 왕실의 어둠을 살필 테니, 춘양 자네는 저들과 함께 고통받는 세상을 구하는 아름다운 여정을 계속 이어가 주시게. 내 너희의 여정에 보탬이 되길 바라며 이 쌀과 꿀단지를 내어주니, 부디 요긴하게 쓰이길 바란다."</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="26" t="inlineStr">
-        <is>
-          <t>character_Chunyang_09</t>
-        </is>
-      </c>
-      <c r="B36" s="25" t="inlineStr">
-        <is>
-          <t>춘양</t>
-        </is>
-      </c>
-      <c r="C36" s="26" t="inlineStr">
-        <is>
-          <t>"(흐르는 눈물을 닦고 입을 가리며 수줍게 미소 짓는다) 나으리의 깊은 뜻을 어찌 거스르겠나이다. 서방님께서 주신 영약과 이 비단결 같은 동료들이 있으니, 제 앞길에 두려울 것이 없사옵니다. 부디 몸조심하시옵소서. 이 모험의 끝에서, 더 밝아진 세상에서 반드시 다시 만나기를 기약하겠나이다."</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="30" t="inlineStr">
-        <is>
-          <t>character_Sangun_01</t>
-        </is>
-      </c>
-      <c r="B37" s="30" t="inlineStr">
-        <is>
-          <t>산군</t>
-        </is>
-      </c>
-      <c r="C37" s="30" t="inlineStr">
-        <is>
-          <t>“어흥—! 떡 하나 주면 안 잡아먹지!”</t>
-        </is>
-      </c>
-      <c r="D37" s="31" t="inlineStr"/>
-      <c r="E37" s="31" t="inlineStr"/>
-      <c r="F37" s="31" t="inlineStr"/>
-      <c r="G37" s="31" t="inlineStr"/>
-      <c r="H37" s="31" t="inlineStr"/>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="30" t="inlineStr">
-        <is>
-          <t>character_Sangun_02</t>
-        </is>
-      </c>
-      <c r="B38" s="30" t="inlineStr">
-        <is>
-          <t>산군</t>
-        </is>
-      </c>
-      <c r="C38" s="30" t="inlineStr">
-        <is>
-          <t>“웬 똥개 한 마리가 감히 내 앞길을 막아서고 짖는단 말이냐? 하하하! 하룻강아지 범 무서운 줄 모른다더니, 딱 너를 두고 하는 말이로구나!”</t>
-        </is>
-      </c>
-      <c r="D38" s="31" t="inlineStr">
-        <is>
-          <t>character_Moran_08</t>
-        </is>
-      </c>
-      <c r="E38" s="31" t="inlineStr"/>
-      <c r="F38" s="31" t="inlineStr"/>
-      <c r="G38" s="31" t="inlineStr"/>
-      <c r="H38" s="31" t="inlineStr"/>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="30" t="inlineStr">
-        <is>
-          <t>character_Moran_08</t>
-        </is>
-      </c>
-      <c r="B39" s="30" t="inlineStr">
-        <is>
-          <t>모란</t>
-        </is>
-      </c>
-      <c r="C39" s="30" t="inlineStr">
-        <is>
-          <t>“먹을 것을 달라면 만들어 드릴 수 있습니다. 다만 사람을 해치는 일은 멈춰 주십시오.”</t>
-        </is>
-      </c>
-      <c r="D39" s="31" t="inlineStr">
-        <is>
-          <t>character_Sangun_03</t>
-        </is>
-      </c>
-      <c r="E39" s="31" t="inlineStr"/>
-      <c r="F39" s="31" t="inlineStr"/>
-      <c r="G39" s="31" t="inlineStr"/>
-      <c r="H39" s="31" t="inlineStr"/>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="30" t="inlineStr">
-        <is>
-          <t>character_Sangun_03</t>
-        </is>
-      </c>
-      <c r="B40" s="30" t="inlineStr">
-        <is>
-          <t>산군</t>
-        </is>
-      </c>
-      <c r="C40" s="30" t="inlineStr">
-        <is>
-          <t>“크흐흡…… 조그만 녀석이 제법 당차구나. 좋다! 어디 그 황금 꿀떡이라는 것을 당장 만들어 보거라. 만약 내 입에 맞지 않으면…… 알지?”</t>
-        </is>
-      </c>
-      <c r="D40" s="31" t="inlineStr"/>
-      <c r="E40" s="31" t="inlineStr"/>
-      <c r="F40" s="31" t="inlineStr"/>
-      <c r="G40" s="31" t="inlineStr"/>
-      <c r="H40" s="31" t="inlineStr"/>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="30" t="inlineStr">
-        <is>
-          <t>character_Sangun_04</t>
-        </is>
-      </c>
-      <c r="B41" s="30" t="inlineStr">
-        <is>
-          <t>산군</t>
-        </is>
-      </c>
-      <c r="C41" s="30" t="inlineStr">
-        <is>
-          <t>“어흐응……! 내 평생 이토록 달콤하고 쫄깃한 떡은 처음이로구나. 사람을 해치며 날뛰던 가슴속 불길이 온데간데없이 가라앉는구나. 미안한 마음을 담아, 깊은 숲의 기운을 머금은 당근을 줄 터이니 받아 가거라.”</t>
-        </is>
-      </c>
-      <c r="D41" s="31" t="inlineStr"/>
-      <c r="E41" s="31" t="inlineStr"/>
-      <c r="F41" s="31" t="inlineStr"/>
-      <c r="G41" s="31" t="inlineStr"/>
-      <c r="H41" s="31" t="inlineStr"/>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="29" t="n"/>
-      <c r="B42" s="29" t="n"/>
-      <c r="C42" s="29" t="n"/>
-      <c r="D42" s="29" t="n"/>
-      <c r="E42" s="29" t="n"/>
-      <c r="F42" s="29" t="n"/>
-      <c r="G42" s="29" t="n"/>
-      <c r="H42" s="29" t="n"/>
-    </row>
-    <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1"/>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="1" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="13" customHeight="1">
+      <c r="A2" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" s="11" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A3" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="22" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+    </row>
+    <row r="5" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+    </row>
+    <row r="6" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+    </row>
+    <row r="7" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+    </row>
+    <row r="8" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+    </row>
+    <row r="9" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A9" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+    </row>
+    <row r="10" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+    </row>
+    <row r="11" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+    </row>
+    <row r="12" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+    </row>
+    <row r="13" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+    </row>
+    <row r="14" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A14" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+    </row>
+    <row r="15" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+    </row>
+    <row r="16" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A16" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A17" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A18" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A19" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A20" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A21" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A22" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A23" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A24" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A25" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A26" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E26" s="4"/>
+    </row>
+    <row r="27" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A27" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A28" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B28" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A29" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B29" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E29" s="4"/>
+    </row>
+    <row r="30" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A30" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B30" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A31" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A32" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B32" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A33" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B33" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A34" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B34" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A35" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B35" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A36" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="B36" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" s="26" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A37" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B37" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="C37" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29"/>
+    </row>
+    <row r="38" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A38" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="B38" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="C38" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="D38" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="E38" s="29"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="29"/>
+      <c r="H38" s="29"/>
+    </row>
+    <row r="39" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A39" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="B39" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="D39" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="E39" s="29"/>
+      <c r="F39" s="29"/>
+      <c r="G39" s="29"/>
+      <c r="H39" s="29"/>
+    </row>
+    <row r="40" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A40" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="B40" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="C40" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="D40" s="29"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="29"/>
+    </row>
+    <row r="41" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A41" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="B41" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="C41" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="D41" s="29"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="29"/>
+      <c r="G41" s="29"/>
+      <c r="H41" s="29"/>
+    </row>
+    <row r="42" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A42" s="27"/>
+      <c r="B42" s="27"/>
+      <c r="C42" s="27"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="27"/>
+      <c r="G42" s="27"/>
+      <c r="H42" s="27"/>
+    </row>
+    <row r="43" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="44" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="45" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="46" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="47" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="48" spans="1:8" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
@@ -2477,7 +2453,8 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/OO_Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Dialogue.xlsx
@@ -317,9 +317,6 @@
     <t>“크흐흡…… 조그만 녀석이 제법 당차구나. 좋다! 어디 그 황금 꿀떡이라는 것을 당장 만들어 보거라. 만약 내 입에 맞지 않으면…… 알지?”</t>
   </si>
   <si>
-    <t>character_Sangun_04</t>
-  </si>
-  <si>
     <t>“어흐응……! 내 평생 이토록 달콤하고 쫄깃한 떡은 처음이로구나. 사람을 해치며 날뛰던 가슴속 불길이 온데간데없이 가라앉는구나. 미안한 마음을 담아, 깊은 숲의 기운을 머금은 당근을 줄 터이니 받아 가거라.”</t>
   </si>
   <si>
@@ -332,6 +329,10 @@
   </si>
   <si>
     <t>character_Sangun_02</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Sangun_04</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1402,13 +1403,13 @@
     </row>
     <row r="37" spans="1:8" ht="15.75" customHeight="1">
       <c r="A37" s="28" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B37" s="28" t="s">
         <v>94</v>
       </c>
       <c r="C37" s="28" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D37" s="29"/>
       <c r="E37" s="29"/>
@@ -1418,7 +1419,7 @@
     </row>
     <row r="38" spans="1:8" ht="15.75" customHeight="1">
       <c r="A38" s="28" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B38" s="28" t="s">
         <v>94</v>
@@ -1470,13 +1471,13 @@
     </row>
     <row r="41" spans="1:8" ht="15.75" customHeight="1">
       <c r="A41" s="28" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B41" s="28" t="s">
         <v>94</v>
       </c>
       <c r="C41" s="28" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D41" s="29"/>
       <c r="E41" s="29"/>

--- a/JsonConverter/ExcelFiles/OO_Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Dialogue.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="108">
   <si>
     <t>대사 ID</t>
   </si>
@@ -293,9 +293,6 @@
     <t>"나는 이곳에 남아 흩어진 민심을 바로잡고 왕실의 어둠을 살필 테니, 춘양 자네는 저들과 함께 고통받는 세상을 구하는 아름다운 여정을 계속 이어가 주시게. 내 너희의 여정에 보탬이 되길 바라며 이 쌀과 꿀단지를 내어주니, 부디 요긴하게 쓰이길 바란다."</t>
   </si>
   <si>
-    <t>character_Chunyang_09</t>
-  </si>
-  <si>
     <t>"(흐르는 눈물을 닦고 입을 가리며 수줍게 미소 짓는다) 나으리의 깊은 뜻을 어찌 거스르겠나이다. 서방님께서 주신 영약과 이 비단결 같은 동료들이 있으니, 제 앞길에 두려울 것이 없사옵니다. 부디 몸조심하시옵소서. 이 모험의 끝에서, 더 밝아진 세상에서 반드시 다시 만나기를 기약하겠나이다."</t>
   </si>
   <si>
@@ -334,6 +331,33 @@
   <si>
     <t>character_Sangun_04</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Chunyang_09</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>character_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Turtle_01</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>거북이</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>“아이고, 이보시오 요리사 양반! 용왕님의 병을 고치려면 저 얄미운 토끼 녀석의 간이 절실히 필요하다오. 달리기 경주로 담판을 지으려 했건만, 발이 어찌나 빠른지 등껍질이 터지도록 뛰어도 도저히 잡을 수가 없으니 내 신세가 처량하구려…….”</t>
   </si>
 </sst>
 </file>
@@ -1392,24 +1416,24 @@
     </row>
     <row r="36" spans="1:8" ht="15.75" customHeight="1">
       <c r="A36" s="26" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="B36" s="25" t="s">
         <v>27</v>
       </c>
       <c r="C36" s="26" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="15.75" customHeight="1">
       <c r="A37" s="28" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B37" s="28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C37" s="28" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D37" s="29"/>
       <c r="E37" s="29"/>
@@ -1419,16 +1443,16 @@
     </row>
     <row r="38" spans="1:8" ht="15.75" customHeight="1">
       <c r="A38" s="28" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B38" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="C38" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="C38" s="28" t="s">
+      <c r="D38" s="29" t="s">
         <v>95</v>
-      </c>
-      <c r="D38" s="29" t="s">
-        <v>96</v>
       </c>
       <c r="E38" s="29"/>
       <c r="F38" s="29"/>
@@ -1437,16 +1461,16 @@
     </row>
     <row r="39" spans="1:8" ht="15.75" customHeight="1">
       <c r="A39" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B39" s="28" t="s">
         <v>18</v>
       </c>
       <c r="C39" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="D39" s="29" t="s">
         <v>97</v>
-      </c>
-      <c r="D39" s="29" t="s">
-        <v>98</v>
       </c>
       <c r="E39" s="29"/>
       <c r="F39" s="29"/>
@@ -1455,13 +1479,13 @@
     </row>
     <row r="40" spans="1:8" ht="15.75" customHeight="1">
       <c r="A40" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="B40" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="C40" s="28" t="s">
         <v>98</v>
-      </c>
-      <c r="B40" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="C40" s="28" t="s">
-        <v>99</v>
       </c>
       <c r="D40" s="29"/>
       <c r="E40" s="29"/>
@@ -1471,13 +1495,13 @@
     </row>
     <row r="41" spans="1:8" ht="15.75" customHeight="1">
       <c r="A41" s="28" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B41" s="28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C41" s="28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D41" s="29"/>
       <c r="E41" s="29"/>
@@ -1495,7 +1519,17 @@
       <c r="G42" s="27"/>
       <c r="H42" s="27"/>
     </row>
-    <row r="43" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="43" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A43" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="B43" s="25" t="s">
+        <v>106</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>107</v>
+      </c>
+    </row>
     <row r="44" spans="1:8" ht="15.75" customHeight="1"/>
     <row r="45" spans="1:8" ht="15.75" customHeight="1"/>
     <row r="46" spans="1:8" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/OO_Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Dialogue.xlsx
@@ -1,451 +1,106 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="12770" yWindow="2240" windowWidth="19820" windowHeight="18420"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="12770" yWindow="2240" windowWidth="19820" windowHeight="18420" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="DNTable_Dialogue" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DNTable_Dialogue" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="108">
-  <si>
-    <t>대사 ID</t>
-  </si>
-  <si>
-    <t>화자 이름 또는 캐릭터 ID</t>
-  </si>
-  <si>
-    <t>대사 내용</t>
-  </si>
-  <si>
-    <t>다음 대사 ID</t>
-  </si>
-  <si>
-    <t>선택지 이름 목록(| 구분)</t>
-  </si>
-  <si>
-    <t>선택지 이동 대사 ID 목록(| 구분)</t>
-  </si>
-  <si>
-    <t>캐릭터 일러스트 경로</t>
-  </si>
-  <si>
-    <t>음성 파일 경로</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>SpeakerName</t>
-  </si>
-  <si>
-    <t>Text</t>
-  </si>
-  <si>
-    <t>NextDialogueId</t>
-  </si>
-  <si>
-    <t>SelectionNameList</t>
-  </si>
-  <si>
-    <t>SelectionDialogueIdList</t>
-  </si>
-  <si>
-    <t>TexturePath</t>
-  </si>
-  <si>
-    <t>VoicePath</t>
-  </si>
-  <si>
-    <t>character_Moran_01</t>
-  </si>
-  <si>
-    <t>모란</t>
-  </si>
-  <si>
-    <t>"치.직... 시.스.템. 가.동. 아.버.지! 저. 말.도. 하.고. 움.직.여.요. 가.슴.속. 태.엽.이. 진짜. 심.장. 처.럼. 쿵.쾅.거.립.니.다. 소.녀. 다.시. 인.사. 올.려.드.리.옵.니.다."</t>
-  </si>
-  <si>
-    <t>character_JangYoungSim_01</t>
-  </si>
-  <si>
-    <t>장영심</t>
-  </si>
-  <si>
-    <t>“……장, 장금아……! 네가 정녕 돌아온 것이냐……!”</t>
-  </si>
-  <si>
-    <t>character_Mr.Jaeik_01</t>
-  </si>
-  <si>
-    <t>재익군</t>
-  </si>
-  <si>
-    <t>"끄응…! 어이쿠, 이 맛은 당최 무엇이구멍유?! 가슴 깊은 곳에서 뜨거운 기운이 확 솟구치는구멍! ……어라? 내, 내가 왜 두 발로 서 있는 거래유? 게다가 사람 말이 입 밖으로 막 나오잖습지멍?! 아이고 대감 천지신명이시여, 이게 무슨 기적이란 말이멍유!"</t>
-  </si>
-  <si>
-    <t>character_Chunyang_01</t>
-  </si>
-  <si>
-    <t>춘양</t>
-  </si>
-  <si>
-    <t>“재익아! 네 이놈, 어디 갔나 했더니 여기서 뭘 먹고…… 아니, 네가 어찌 사람의 옷을 입고 두 발로 서 있는 게냐? 귀신이 곡할 노릇이로구나!”</t>
-  </si>
-  <si>
-    <t>character_Mr.Jaeik_02</t>
-  </si>
-  <si>
-    <t>“아씨! 글쎄 이 신비로운 요리를 한 입 먹었더니만, 온몸의 털이 곤두서며 진짜로 말하는 사람이 되었구멍요!”</t>
-  </si>
-  <si>
-    <t>character_Moran_02</t>
-  </si>
-  <si>
-    <t>“안녕하세요, 여러분! 음식으로 세상을 치유하는 멋진 여정을 떠나보려고 해요. 제 동료가 되어서 이 모험을 함께해 주시지 않겠어요?”</t>
-  </si>
-  <si>
-    <t>character_Chunyang_02</t>
-  </si>
-  <si>
-    <t>“나는 홀연히 자취를 감춘 서방님, 몽령 나으리를 찾기 위해 온 팔도를 헤매는 중이라오. 갈 길이 멀고 험난한 여정이 되겠으나…… 그대들의 이 신비로운 음식을 여정 내내 맛볼 수만 있다면, 내 기꺼이 길잡이가 되어 드리겠소.”</t>
-  </si>
-  <si>
-    <t>character_Chunyang_03</t>
-  </si>
-  <si>
-    <t>“우리 아버님께서 내어주신 참으로 귀한 쌀이라오. 자네들의 여정에 조금이나마 보탬이 되었으면 좋겠소.”</t>
-  </si>
-  <si>
-    <t>character_Moran_03</t>
-  </si>
-  <si>
-    <t>“우리 집 마당에서 기른 귀한 채소들이에요. 참 맛좋은 음식들이 가득했었는데… 아쉽게도 다른 음식은 재익 군이 남김없이 다 먹어버렸지요! 하하.”</t>
-  </si>
-  <si>
-    <t>character_Mr.Jaeik_03</t>
-  </si>
-  <si>
-    <t>“아이고, 모란님… 면목이 없구멍유. 그 참을 수 없는 냄새에 저도 모르게 개 버릇을 못 고치고 주둥이가 먼저 나가버렸지 멍유……. 정말 미안하구멍유…….”</t>
-  </si>
-  <si>
-    <t>character_Chunyang_04</t>
-  </si>
-  <si>
-    <t>“모란님, 이 미련한 놈의 허물은 내 대신 사죄하겠소. 밥값을 하려면 부지런히 길을 나서야 할 터…… 먼저는 동쪽으로 가시지요. 그곳에 탐관오리의 수탈로 배 굶주린 자들이 유독 많다 들었습니다.”</t>
-  </si>
-  <si>
-    <t>character_Mr.Jaeik_04</t>
-  </si>
-  <si>
-    <t>“슬슬 날이 저무니 배가 고프지 않습니까요, 아씨? 제가 배고파서 그런 건 절대 아니구멍유……! 모란 님이 우리를 위해 맛난 요리를 해주신다면 참말로 감사하겠서요!”
-(그의 꼬리를 흔들리는걸 멈추지 않는 탓일가)</t>
-  </si>
-  <si>
-    <t>character_Chunyang_05</t>
-  </si>
-  <si>
-    <t>“그러고 보니 벌써 저녁때가 되었구려. 마침 다들 지쳤을 터인데, 낭자에게 염치 불고하고 따뜻한 식사를 부탁드려도 되겠소?”</t>
-  </si>
-  <si>
-    <t>character_Moran_04</t>
-  </si>
-  <si>
-    <t>“당연히 해드려야죠! 가마솥을 뜨겁게 달굴 테니, 두 분 다 조금만 기다려주세요. 세상에서 가장 배부른 요리를 지어드릴게요!”</t>
-  </si>
-  <si>
-    <t>character_Moran_05</t>
-  </si>
-  <si>
-    <t>“따끈따끈한 ‘야채죽’이 완성되었어요! 소박하지만 지친 몸을 따뜻하게 데워줄 거예요. 어서 맛있게 드세요!”</t>
-  </si>
-  <si>
-    <t>character_VillageChief_01</t>
-  </si>
-  <si>
-    <t>촌장</t>
-  </si>
-  <si>
-    <t>“포학한 왕이 보낸 탐관오리들이 가호마다 뼛속까지 수탈해 가니, 이제 우리 마을엔 들쥐 새끼 한 마리 먹을 것조차 남지 않았소. 백성들이 길가에 쓰러져 굶어 죽어가는 실정이오……. 부디, 오늘 단 하루만이라도 이 지친 이들의 주린 배를 달래줄 따뜻한 온기 한 그릇을 나누어 줄 수 없겠소?”</t>
-  </si>
-  <si>
-    <t>character_VillageChief_02</t>
-  </si>
-  <si>
-    <t>“허어, 눈물이 앞을 가리는구려…… 이 은혜를 어찌 다 갚아야 할지 모르겠소. 비록 지금은 척박해진 땅이나, 매서운 추위도 잊게 만드는 우리 마을의 오랜 특산물인 청양고추라오. 모란님의 앞날에 작게나마 보탬이 되길 바라오.”</t>
-  </si>
-  <si>
-    <t>character_Chunyang_06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">춘양 </t>
-  </si>
-  <si>
-    <t>“이런 횡포를 부린 자인 탐관오리에게 가셔서 담판을 내시죠, 모란님.”</t>
-  </si>
-  <si>
-    <t>character_Mr.Jaeik_05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">재익군 </t>
-  </si>
-  <si>
-    <t>“아씨~! 탐관오리란 자가 얼마나 무서운 자인디 굳이 거길 가시려 하십니까유? 지금은 저희를 지켜줄 이몽령 도련님도 안 계신단 마류~!”</t>
-  </si>
-  <si>
-    <t>character_Chunyang_07</t>
-  </si>
-  <si>
-    <t>“네 이놈! 감히 그 주둥이에 내 서방님의 이름을 함부로 올리지 마라!”</t>
-  </si>
-  <si>
-    <t>character_Mr.Jaeik_06</t>
-  </si>
-  <si>
-    <t>“이익!!! 죄송하구멍유! (깜짝 놀라 읍! 하고 앞 발이였던 손으로 입을 틀어막는다)”</t>
-  </si>
-  <si>
-    <t>character_Moran_06</t>
-  </si>
-  <si>
-    <t>“춘양 아씨, 너무 마음 쓰지 마세요. 도련님을 향한 아씨의 깊은 마음을 재익이가 미처 몰라보고 말실수를 한 모양입니다. 재익군, 무서운 건 당연하지만 우리가 힘을 합치면 괜찮을 거야. 촌장님이 주신 청양고추도 있으니 기운 내서 수레를 움직여볼까?”</t>
-  </si>
-  <si>
-    <t>character_GreedyDuck_01</t>
-  </si>
-  <si>
-    <t>탐관오리</t>
-  </si>
-  <si>
-    <t>“네 이놈들! 감히 내 수청을 들지 않고 도망친 춘양을 숨겨준 것도 모자라, 요상한 수레로 천한 백성들을 선동하며 내 호박들을 훔쳐가다니! 당장 저 고약한 역적 놈들을 포박하라!”</t>
-  </si>
-  <si>
-    <t>character_GreedyDuck_02</t>
-  </si>
-  <si>
-    <t>"저건 또 어디서 굴러먹다 온 거렁뱅이 놈이냐! 감히 이 귀한 곳에 함부로 발을 디디다니! 여봐라, 저 고얀 놈까지 당장 포승줄로 꽁꽁 묶어라! 저 발칙한 역적 패당 네 놈과 함께 볼기를 곤장으로 매우 쳐……!"</t>
-  </si>
-  <si>
-    <t>character_LeeMongRyong_01</t>
-  </si>
-  <si>
-    <t>이몽령</t>
-  </si>
-  <si>
-    <t>“암행어사 출두야—! 백성들의 고혈을 짜내어 자신의 배만 불리던 탐관오리 놈아, 네 죄를 네가 알렷다!"</t>
-  </si>
-  <si>
-    <t>character_LeeMongRyong_02</t>
-  </si>
-  <si>
-    <t>"모란아, 네 소문은 익히 들었다. 이 자를 벌 하기 위한 음식을 만들어보려구나.”</t>
-  </si>
-  <si>
-    <t>character_Moran_07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">모란 </t>
-  </si>
-  <si>
-    <t>“예, 도련님. 마침 마을 촌장님께 얻은 귀한 청양고추가 있으니, 아주 매콤한 찌개를 끓여 대접하겠습니다.”</t>
-  </si>
-  <si>
-    <t>character_GreedyDuck_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">탐관오리 </t>
-  </si>
-  <si>
-    <t>탐관오리: "아이고, 나 죽네! 입안에서 화룡이 불을 뿜는구나!! 물! 당장 물을 가져오너라어어억—!!"</t>
-  </si>
-  <si>
-    <t>character_LeeMongRyong_03</t>
-  </si>
-  <si>
-    <t>(떠내려가는 탐관오리를 보며 헛기침을 하다가, 이내 춘향을 돌아보며) "덕분에 큰 소동 없이 의로운 일을 마쳤소. ……춘양아, 그동안 무탈하였느냐. 내 오느라 너무 늦었다. 그간 고생이 많았구나."</t>
-  </si>
-  <si>
-    <t>character_Chunyang_08</t>
-  </si>
-  <si>
-    <t>"나으리…… 밤낮으로 오직 서방님만을 그리워하며 이 모진 시간을 버텨왔나이다."</t>
-  </si>
-  <si>
-    <t xml:space="preserve">character_LeeMongRyong_04 </t>
-  </si>
-  <si>
-    <t>"(춘양을 따뜻하게 바라보며) "참으로 비단결 같은 마음을 가진 동료들과 함께하고 있구나."</t>
-  </si>
-  <si>
-    <t>character_LeeMongRyong_05</t>
-  </si>
-  <si>
-    <t>"나는 이곳에 남아 흩어진 민심을 바로잡고 왕실의 어둠을 살필 테니, 춘양 자네는 저들과 함께 고통받는 세상을 구하는 아름다운 여정을 계속 이어가 주시게. 내 너희의 여정에 보탬이 되길 바라며 이 쌀과 꿀단지를 내어주니, 부디 요긴하게 쓰이길 바란다."</t>
-  </si>
-  <si>
-    <t>"(흐르는 눈물을 닦고 입을 가리며 수줍게 미소 짓는다) 나으리의 깊은 뜻을 어찌 거스르겠나이다. 서방님께서 주신 영약과 이 비단결 같은 동료들이 있으니, 제 앞길에 두려울 것이 없사옵니다. 부디 몸조심하시옵소서. 이 모험의 끝에서, 더 밝아진 세상에서 반드시 다시 만나기를 기약하겠나이다."</t>
-  </si>
-  <si>
-    <t>산군</t>
-  </si>
-  <si>
-    <t>“웬 똥개 한 마리가 감히 내 앞길을 막아서고 짖는단 말이냐? 하하하! 하룻강아지 범 무서운 줄 모른다더니, 딱 너를 두고 하는 말이로구나!”</t>
-  </si>
-  <si>
-    <t>character_Moran_08</t>
-  </si>
-  <si>
-    <t>“먹을 것을 달라면 만들어 드릴 수 있습니다. 다만 사람을 해치는 일은 멈춰 주십시오.”</t>
-  </si>
-  <si>
-    <t>character_Sangun_03</t>
-  </si>
-  <si>
-    <t>“크흐흡…… 조그만 녀석이 제법 당차구나. 좋다! 어디 그 황금 꿀떡이라는 것을 당장 만들어 보거라. 만약 내 입에 맞지 않으면…… 알지?”</t>
-  </si>
-  <si>
-    <t>“어흐응……! 내 평생 이토록 달콤하고 쫄깃한 떡은 처음이로구나. 사람을 해치며 날뛰던 가슴속 불길이 온데간데없이 가라앉는구나. 미안한 마음을 담아, 깊은 숲의 기운을 머금은 당근을 줄 터이니 받아 가거라.”</t>
-  </si>
-  <si>
-    <t>“어흥—! 떡 하나 주면 안 잡아먹지!”</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>character_Sangun_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>character_Sangun_02</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>character_Sangun_04</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>character_Chunyang_09</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>character_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Turtle_01</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>거북이</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>“아이고, 이보시오 요리사 양반! 용왕님의 병을 고치려면 저 얄미운 토끼 녀석의 간이 절실히 필요하다오. 달리기 경주로 담판을 지으려 했건만, 발이 어찌나 빠른지 등껍질이 터지도록 뛰어도 도저히 잡을 수가 없으니 내 신세가 처량하구려…….”</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="12">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="13">
     <font>
+      <name val="Arial"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="&quot;맑은 고딕&quot;"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="&quot;맑은 고딕&quot;"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="8"/>
-      <name val="Arial"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="돋움"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color theme="1"/>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
+      <name val="돋움"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="?? ??"/>
       <sz val="10"/>
-      <name val="?? ??"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="10"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="14">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -476,7 +131,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="7" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -498,6 +153,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -543,78 +213,161 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="37">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -815,731 +568,1207 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1000"/>
-  <sheetFormatPr defaultColWidth="17" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:O53"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="17" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="14" style="2" customWidth="1"/>
-    <col min="2" max="2" width="21" style="2" customWidth="1"/>
-    <col min="3" max="4" width="14" style="2" customWidth="1"/>
-    <col min="5" max="5" width="21" style="2" customWidth="1"/>
-    <col min="6" max="6" width="27" style="2" customWidth="1"/>
-    <col min="7" max="7" width="17" style="2" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="17" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="17" style="2"/>
+    <col width="27" customWidth="1" style="2" min="1" max="1"/>
+    <col width="17" customWidth="1" style="2" min="2" max="2"/>
+    <col width="42" customWidth="1" style="2" min="3" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" style="2" min="5" max="5"/>
+    <col width="25" customWidth="1" style="2" min="6" max="6"/>
+    <col width="13" customWidth="1" style="2" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" style="2" min="9" max="9"/>
+    <col width="12" customWidth="1" style="2" min="10" max="16384"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A1" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="18" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="13" customHeight="1">
-      <c r="A2" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="20" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" s="11" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A3" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="22" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-    </row>
-    <row r="5" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-    </row>
-    <row r="6" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-    </row>
-    <row r="7" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-    </row>
-    <row r="8" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A8" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-    </row>
-    <row r="9" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A9" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-    </row>
-    <row r="10" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-    </row>
-    <row r="11" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-    </row>
-    <row r="12" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A12" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-    </row>
-    <row r="13" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A13" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-    </row>
-    <row r="14" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A14" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
-    </row>
-    <row r="15" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A15" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
-    </row>
-    <row r="16" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A16" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A17" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A18" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A19" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-    </row>
-    <row r="20" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A20" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A21" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A22" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A23" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="B23" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A24" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="B24" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A25" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="E25" s="4"/>
-    </row>
-    <row r="26" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A26" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="B26" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E26" s="4"/>
-    </row>
-    <row r="27" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A27" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B27" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E27" s="4"/>
-    </row>
-    <row r="28" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A28" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="B28" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E28" s="4"/>
-    </row>
-    <row r="29" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A29" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B29" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="E29" s="4"/>
-    </row>
-    <row r="30" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A30" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="B30" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A31" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A32" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="B32" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A33" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="B33" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A34" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="B34" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A35" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="B35" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A36" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="B36" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="C36" s="26" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A37" s="28" t="s">
-        <v>101</v>
-      </c>
-      <c r="B37" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="C37" s="28" t="s">
-        <v>100</v>
-      </c>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
-      <c r="G37" s="29"/>
-      <c r="H37" s="29"/>
-    </row>
-    <row r="38" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A38" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="B38" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="C38" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="D38" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="E38" s="29"/>
-      <c r="F38" s="29"/>
-      <c r="G38" s="29"/>
-      <c r="H38" s="29"/>
-    </row>
-    <row r="39" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A39" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="B39" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="C39" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="D39" s="29" t="s">
-        <v>97</v>
-      </c>
-      <c r="E39" s="29"/>
-      <c r="F39" s="29"/>
-      <c r="G39" s="29"/>
-      <c r="H39" s="29"/>
-    </row>
-    <row r="40" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A40" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="B40" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="C40" s="28" t="s">
-        <v>98</v>
-      </c>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-    </row>
-    <row r="41" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A41" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="B41" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="C41" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="D41" s="29"/>
-      <c r="E41" s="29"/>
-      <c r="F41" s="29"/>
-      <c r="G41" s="29"/>
-      <c r="H41" s="29"/>
-    </row>
-    <row r="42" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A42" s="27"/>
-      <c r="B42" s="27"/>
-      <c r="C42" s="27"/>
-      <c r="D42" s="27"/>
-      <c r="E42" s="27"/>
-      <c r="F42" s="27"/>
-      <c r="G42" s="27"/>
-      <c r="H42" s="27"/>
-    </row>
-    <row r="43" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A43" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="B43" s="25" t="s">
-        <v>106</v>
-      </c>
-      <c r="C43" s="13" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="47" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="48" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="49" ht="15.75" customHeight="1"/>
-    <row r="50" ht="15.75" customHeight="1"/>
-    <row r="51" ht="15.75" customHeight="1"/>
-    <row r="52" ht="15.75" customHeight="1"/>
-    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>대사 ID</t>
+        </is>
+      </c>
+      <c r="B1" s="31" t="inlineStr">
+        <is>
+          <t>화자 이름 또는 캐릭터 ID</t>
+        </is>
+      </c>
+      <c r="C1" s="31" t="inlineStr">
+        <is>
+          <t>대사 내용</t>
+        </is>
+      </c>
+      <c r="D1" s="31" t="inlineStr">
+        <is>
+          <t>다음 대사 ID</t>
+        </is>
+      </c>
+      <c r="E1" s="31" t="inlineStr">
+        <is>
+          <t>선택지 이름 목록(| 구분)</t>
+        </is>
+      </c>
+      <c r="F1" s="32" t="inlineStr">
+        <is>
+          <t>선택지 이동 대사 ID 목록(| 구분)</t>
+        </is>
+      </c>
+      <c r="G1" s="32" t="inlineStr">
+        <is>
+          <t>캐릭터 일러스트 경로</t>
+        </is>
+      </c>
+      <c r="H1" s="32" t="inlineStr">
+        <is>
+          <t>음성 파일 경로</t>
+        </is>
+      </c>
+      <c r="I1" s="32" t="n"/>
+      <c r="J1" s="32" t="n"/>
+      <c r="K1" s="32" t="n"/>
+      <c r="L1" s="32" t="n"/>
+      <c r="M1" s="32" t="n"/>
+      <c r="N1" s="32" t="n"/>
+      <c r="O1" s="32" t="n"/>
+    </row>
+    <row r="2" ht="13" customHeight="1">
+      <c r="A2" s="33" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="B2" s="33" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" s="33" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" s="33" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" s="33" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" s="33" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G2" s="34" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H2" s="34" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I2" s="34" t="n"/>
+      <c r="J2" s="34" t="n"/>
+      <c r="K2" s="34" t="n"/>
+      <c r="L2" s="34" t="n"/>
+      <c r="M2" s="34" t="n"/>
+      <c r="N2" s="34" t="n"/>
+      <c r="O2" s="34" t="n"/>
+    </row>
+    <row r="3" ht="15.75" customFormat="1" customHeight="1" s="11">
+      <c r="A3" s="35" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="B3" s="35" t="inlineStr">
+        <is>
+          <t>SpeakerName</t>
+        </is>
+      </c>
+      <c r="C3" s="35" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D3" s="35" t="inlineStr">
+        <is>
+          <t>NextDialogueId</t>
+        </is>
+      </c>
+      <c r="E3" s="35" t="inlineStr">
+        <is>
+          <t>SelectionNameList</t>
+        </is>
+      </c>
+      <c r="F3" s="35" t="inlineStr">
+        <is>
+          <t>SelectionDialogueIdList</t>
+        </is>
+      </c>
+      <c r="G3" s="36" t="inlineStr">
+        <is>
+          <t>TexturePath</t>
+        </is>
+      </c>
+      <c r="H3" s="36" t="inlineStr">
+        <is>
+          <t>VoicePath</t>
+        </is>
+      </c>
+      <c r="I3" s="36" t="n"/>
+      <c r="J3" s="36" t="n"/>
+      <c r="K3" s="36" t="n"/>
+      <c r="L3" s="36" t="n"/>
+      <c r="M3" s="36" t="n"/>
+      <c r="N3" s="36" t="n"/>
+      <c r="O3" s="36" t="n"/>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>character_Moran_01</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>모란</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>"치.직... 시.스.템. 가.동. 아.버.지! 저. 말.도. 하.고. 움.직.여.요. 가.슴.속. 태.엽.이. 진짜. 심.장. 처.럼. 쿵.쾅.거.립.니.다. 소.녀. 다.시. 인.사. 올.려.드.리.옵.니.다."</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="12" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="4" t="n"/>
+      <c r="O4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>character_JangYoungSim_01</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>장영심</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>“……장, 장금아……! 네가 정녕 돌아온 것이냐……!”</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>character_Mr.Jaeik_01</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>재익군</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>"끄응…! 어이쿠, 이 맛은 당최 무엇이구멍유?! 가슴 깊은 곳에서 뜨거운 기운이 확 솟구치는구멍! ……어라? 내, 내가 왜 두 발로 서 있는 거래유? 게다가 사람 말이 입 밖으로 막 나오잖습지멍?! 아이고 대감 천지신명이시여, 이게 무슨 기적이란 말이멍유!"</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>character_Chunyang_01</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>춘양</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>“재익아! 네 이놈, 어디 갔나 했더니 여기서 뭘 먹고…… 아니, 네가 어찌 사람의 옷을 입고 두 발로 서 있는 게냐? 귀신이 곡할 노릇이로구나!”</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="n"/>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="4" t="n"/>
+      <c r="K7" s="4" t="n"/>
+      <c r="L7" s="4" t="n"/>
+      <c r="M7" s="4" t="n"/>
+      <c r="N7" s="4" t="n"/>
+      <c r="O7" s="4" t="n"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>character_Mr.Jaeik_02</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>재익군</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>“아씨! 글쎄 이 신비로운 요리를 한 입 먹었더니만, 온몸의 털이 곤두서며 진짜로 말하는 사람이 되었구멍요!”</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="n"/>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="4" t="n"/>
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="4" t="n"/>
+      <c r="M8" s="4" t="n"/>
+      <c r="N8" s="4" t="n"/>
+      <c r="O8" s="4" t="n"/>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>character_Moran_02</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>모란</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>“안녕하세요, 여러분! 음식으로 세상을 치유하는 멋진 여정을 떠나보려고 해요. 제 동료가 되어서 이 모험을 함께해 주시지 않겠어요?”</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="n"/>
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="4" t="n"/>
+      <c r="I9" s="4" t="n"/>
+      <c r="J9" s="4" t="n"/>
+      <c r="K9" s="4" t="n"/>
+      <c r="L9" s="4" t="n"/>
+      <c r="M9" s="4" t="n"/>
+      <c r="N9" s="4" t="n"/>
+      <c r="O9" s="4" t="n"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>character_Chunyang_02</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>춘양</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>“나는 홀연히 자취를 감춘 서방님, 몽령 나으리를 찾기 위해 온 팔도를 헤매는 중이라오. 갈 길이 멀고 험난한 여정이 되겠으나…… 그대들의 이 신비로운 음식을 여정 내내 맛볼 수만 있다면, 내 기꺼이 길잡이가 되어 드리겠소.”</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="n"/>
+      <c r="I10" s="4" t="n"/>
+      <c r="J10" s="4" t="n"/>
+      <c r="K10" s="4" t="n"/>
+      <c r="L10" s="4" t="n"/>
+      <c r="M10" s="4" t="n"/>
+      <c r="N10" s="4" t="n"/>
+      <c r="O10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>character_Chunyang_03</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>춘양</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>“우리 아버님께서 내어주신 참으로 귀한 쌀이라오. 자네들의 여정에 조금이나마 보탬이 되었으면 좋겠소.”</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="4" t="n"/>
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>character_Moran_03</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>모란</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>“우리 집 마당에서 기른 귀한 채소들이에요. 참 맛좋은 음식들이 가득했었는데… 아쉽게도 다른 음식은 재익 군이 남김없이 다 먹어버렸지요! 하하.”</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n"/>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="4" t="n"/>
+      <c r="K12" s="4" t="n"/>
+      <c r="L12" s="4" t="n"/>
+      <c r="M12" s="4" t="n"/>
+      <c r="N12" s="4" t="n"/>
+      <c r="O12" s="4" t="n"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>character_Mr.Jaeik_03</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>재익군</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>“아이고, 모란님… 면목이 없구멍유. 그 참을 수 없는 냄새에 저도 모르게 개 버릇을 못 고치고 주둥이가 먼저 나가버렸지 멍유……. 정말 미안하구멍유…….”</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="n"/>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="4" t="n"/>
+      <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="n"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>character_Chunyang_04</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>춘양</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>“모란님, 이 미련한 놈의 허물은 내 대신 사죄하겠소. 밥값을 하려면 부지런히 길을 나서야 할 터…… 먼저는 동쪽으로 가시지요. 그곳에 탐관오리의 수탈로 배 굶주린 자들이 유독 많다 들었습니다.”</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="4" t="n"/>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="4" t="n"/>
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>character_Mr.Jaeik_04</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>재익군</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>“슬슬 날이 저무니 배가 고프지 않습니까요, 아씨? 제가 배고파서 그런 건 절대 아니구멍유……! 모란 님이 우리를 위해 맛난 요리를 해주신다면 참말로 감사하겠서요!”
+(그의 꼬리를 흔들리는걸 멈추지 않는 탓일가)</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
+      <c r="H15" s="4" t="n"/>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="4" t="n"/>
+      <c r="K15" s="4" t="n"/>
+      <c r="L15" s="4" t="n"/>
+      <c r="M15" s="4" t="n"/>
+      <c r="N15" s="4" t="n"/>
+      <c r="O15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>character_Chunyang_05</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>춘양</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>“그러고 보니 벌써 저녁때가 되었구려. 마침 다들 지쳤을 터인데, 낭자에게 염치 불고하고 따뜻한 식사를 부탁드려도 되겠소?”</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>character_Moran_04</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>모란</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>“당연히 해드려야죠! 가마솥을 뜨겁게 달굴 테니, 두 분 다 조금만 기다려주세요. 세상에서 가장 배부른 요리를 지어드릴게요!”</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>character_Moran_05</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>모란</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>“따끈따끈한 ‘야채죽’이 완성되었어요! 소박하지만 지친 몸을 따뜻하게 데워줄 거예요. 어서 맛있게 드세요!”</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>character_VillageChief_01</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>촌장</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>“포학한 왕이 보낸 탐관오리들이 가호마다 뼛속까지 수탈해 가니, 이제 우리 마을엔 들쥐 새끼 한 마리 먹을 것조차 남지 않았소. 백성들이 길가에 쓰러져 굶어 죽어가는 실정이오……. 부디, 오늘 단 하루만이라도 이 지친 이들의 주린 배를 달래줄 따뜻한 온기 한 그릇을 나누어 줄 수 없겠소?”</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>character_VillageChief_02</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>촌장</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>“허어, 눈물이 앞을 가리는구려…… 이 은혜를 어찌 다 갚아야 할지 모르겠소. 비록 지금은 척박해진 땅이나, 매서운 추위도 잊게 만드는 우리 마을의 오랜 특산물인 청양고추라오. 모란님의 앞날에 작게나마 보탬이 되길 바라오.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>character_Chunyang_06</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">춘양 </t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>“이런 횡포를 부린 자인 탐관오리에게 가셔서 담판을 내시죠, 모란님.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>character_Mr.Jaeik_05</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">재익군 </t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>“아씨~! 탐관오리란 자가 얼마나 무서운 자인디 굳이 거길 가시려 하십니까유? 지금은 저희를 지켜줄 이몽령 도련님도 안 계신단 마류~!”</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>character_Chunyang_07</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>춘양</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>“네 이놈! 감히 그 주둥이에 내 서방님의 이름을 함부로 올리지 마라!”</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>character_Mr.Jaeik_06</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>재익군</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>“이익!!! 죄송하구멍유! (깜짝 놀라 읍! 하고 앞 발이였던 손으로 입을 틀어막는다)”</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>character_Moran_06</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>모란</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>“춘양 아씨, 너무 마음 쓰지 마세요. 도련님을 향한 아씨의 깊은 마음을 재익이가 미처 몰라보고 말실수를 한 모양입니다. 재익군, 무서운 건 당연하지만 우리가 힘을 합치면 괜찮을 거야. 촌장님이 주신 청양고추도 있으니 기운 내서 수레를 움직여볼까?”</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="n"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>character_GreedyDuck_01</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>탐관오리</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>“네 이놈들! 감히 내 수청을 들지 않고 도망친 춘양을 숨겨준 것도 모자라, 요상한 수레로 천한 백성들을 선동하며 내 호박들을 훔쳐가다니! 당장 저 고약한 역적 놈들을 포박하라!”</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="n"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>character_GreedyDuck_02</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>탐관오리</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>"저건 또 어디서 굴러먹다 온 거렁뱅이 놈이냐! 감히 이 귀한 곳에 함부로 발을 디디다니! 여봐라, 저 고얀 놈까지 당장 포승줄로 꽁꽁 묶어라! 저 발칙한 역적 패당 네 놈과 함께 볼기를 곤장으로 매우 쳐……!"</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="n"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>character_LeeMongRyong_01</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>이몽령</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>“암행어사 출두야—! 백성들의 고혈을 짜내어 자신의 배만 불리던 탐관오리 놈아, 네 죄를 네가 알렷다!"</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="n"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>character_LeeMongRyong_02</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>이몽령</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>"모란아, 네 소문은 익히 들었다. 이 자를 벌 하기 위한 음식을 만들어보려구나.”</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="n"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>character_Moran_07</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모란 </t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>“예, 도련님. 마침 마을 촌장님께 얻은 귀한 청양고추가 있으니, 아주 매콤한 찌개를 끓여 대접하겠습니다.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>character_GreedyDuck_03</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">탐관오리 </t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>탐관오리: "아이고, 나 죽네! 입안에서 화룡이 불을 뿜는구나!! 물! 당장 물을 가져오너라어어억—!!"</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>character_LeeMongRyong_03</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>이몽령</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>(강으로 달려가는 탐관오리를 보며 헛기침을 하다가, 이내 춘향을 돌아보며) "덕분에 큰 소동 없이 의로운 일을 마쳤소. ……춘양아, 그동안 무탈하였느냐. 내 오느라 너무 늦었다. 그간 고생이 많았구나."</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>character_Chunyang_08</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>춘양</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>"나으리…… 밤낮으로 오직 서방님만을 그리워하며 이 모진 시간을 버텨왔나이다."</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">character_LeeMongRyong_04 </t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>이몽령</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>"(춘양을 따뜻하게 바라보며) "참으로 비단결 같은 마음을 가진 동료들과 함께하고 있구나."</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>character_LeeMongRyong_05</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>이몽령</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>"나는 이곳에 남아 흩어진 민심을 바로잡고 왕실의 어둠을 살필 테니, 춘양 자네는 저들과 함께 고통받는 세상을 구하는 아름다운 여정을 계속 이어가 주시게. 내 너희의 여정에 보탬이 되길 바라며 이 쌀과 꿀단지를 내어주니, 부디 요긴하게 쓰이길 바란다."</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="26" t="inlineStr">
+        <is>
+          <t>character_Chunyang_09</t>
+        </is>
+      </c>
+      <c r="B36" s="25" t="inlineStr">
+        <is>
+          <t>춘양</t>
+        </is>
+      </c>
+      <c r="C36" s="26" t="inlineStr">
+        <is>
+          <t>"나으리의 깊은 뜻을 어찌 거스르겠나이다. 서방님께서 주신 영약과 이 비단결 같은 동료들이 있으니, 제 앞길에 두려울 것이 없사옵니다. 부디 몸조심하시옵소서. 이 모험의 끝에서, 더 밝아진 세상에서 반드시 다시 만나기를 기약하겠나이다."</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="28" t="inlineStr">
+        <is>
+          <t>character_Sangun_01</t>
+        </is>
+      </c>
+      <c r="B37" s="28" t="inlineStr">
+        <is>
+          <t>산군</t>
+        </is>
+      </c>
+      <c r="C37" s="28" t="inlineStr">
+        <is>
+          <t>“어흥—! 떡 하나 주면 안 잡아먹지!”</t>
+        </is>
+      </c>
+      <c r="D37" s="29" t="n"/>
+      <c r="E37" s="29" t="n"/>
+      <c r="F37" s="29" t="n"/>
+      <c r="G37" s="29" t="n"/>
+      <c r="H37" s="29" t="n"/>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="28" t="inlineStr">
+        <is>
+          <t>character_Sangun_02</t>
+        </is>
+      </c>
+      <c r="B38" s="28" t="inlineStr">
+        <is>
+          <t>산군</t>
+        </is>
+      </c>
+      <c r="C38" s="28" t="inlineStr">
+        <is>
+          <t>“웬 똥개 한 마리가 감히 내 앞길을 막아서고 짖는단 말이냐? 하하하! 하룻강아지 범 무서운 줄 모른다더니, 딱 너를 두고 하는 말이로구나!”</t>
+        </is>
+      </c>
+      <c r="D38" s="29" t="inlineStr">
+        <is>
+          <t>character_Moran_08</t>
+        </is>
+      </c>
+      <c r="E38" s="29" t="n"/>
+      <c r="F38" s="29" t="n"/>
+      <c r="G38" s="29" t="n"/>
+      <c r="H38" s="29" t="n"/>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="28" t="inlineStr">
+        <is>
+          <t>character_Moran_08</t>
+        </is>
+      </c>
+      <c r="B39" s="28" t="inlineStr">
+        <is>
+          <t>모란</t>
+        </is>
+      </c>
+      <c r="C39" s="28" t="inlineStr">
+        <is>
+          <t>“먹을 것을 달라면 만들어 드릴 수 있습니다. 다만 사람을 해치는 일은 멈춰 주십시오.”</t>
+        </is>
+      </c>
+      <c r="D39" s="29" t="inlineStr">
+        <is>
+          <t>character_Sangun_03</t>
+        </is>
+      </c>
+      <c r="E39" s="29" t="n"/>
+      <c r="F39" s="29" t="n"/>
+      <c r="G39" s="29" t="n"/>
+      <c r="H39" s="29" t="n"/>
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="A40" s="28" t="inlineStr">
+        <is>
+          <t>character_Sangun_03</t>
+        </is>
+      </c>
+      <c r="B40" s="28" t="inlineStr">
+        <is>
+          <t>산군</t>
+        </is>
+      </c>
+      <c r="C40" s="28" t="inlineStr">
+        <is>
+          <t>“크흐흡…… 조그만 녀석이 제법 당차구나. 좋다! 어디 그 황금 꿀떡이라는 것을 당장 만들어 보거라. 만약 내 입에 맞지 않으면…… 알지?”</t>
+        </is>
+      </c>
+      <c r="D40" s="29" t="n"/>
+      <c r="E40" s="29" t="n"/>
+      <c r="F40" s="29" t="n"/>
+      <c r="G40" s="29" t="n"/>
+      <c r="H40" s="29" t="n"/>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="28" t="inlineStr">
+        <is>
+          <t>character_Sangun_04</t>
+        </is>
+      </c>
+      <c r="B41" s="28" t="inlineStr">
+        <is>
+          <t>산군</t>
+        </is>
+      </c>
+      <c r="C41" s="28" t="inlineStr">
+        <is>
+          <t>“어흐응……! 내 평생 이토록 달콤하고 쫄깃한 떡은 처음이로구나. 사람을 해치며 날뛰던 가슴속 불길이 온데간데없이 가라앉는구나. 미안한 마음을 담아, 깊은 숲의 기운을 머금은 당근을 줄 터이니 받아 가거라.”</t>
+        </is>
+      </c>
+      <c r="D41" s="29" t="n"/>
+      <c r="E41" s="29" t="n"/>
+      <c r="F41" s="29" t="n"/>
+      <c r="G41" s="29" t="n"/>
+      <c r="H41" s="29" t="n"/>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="27" t="n"/>
+      <c r="B42" s="27" t="n"/>
+      <c r="C42" s="27" t="n"/>
+      <c r="D42" s="27" t="n"/>
+      <c r="E42" s="27" t="n"/>
+      <c r="F42" s="27" t="n"/>
+      <c r="G42" s="27" t="n"/>
+      <c r="H42" s="27" t="n"/>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="26" t="inlineStr">
+        <is>
+          <t>character_Turtle_01</t>
+        </is>
+      </c>
+      <c r="B43" s="25" t="inlineStr">
+        <is>
+          <t>거북이</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="inlineStr">
+        <is>
+          <t>“아이고, 이보시오 요리사 양반! 용왕님의 병을 고치려면 저 얄미운 토끼 녀석의 간이 절실히 필요하다오. 달리기 경주로 담판을 지으려 했건만, 발이 어찌나 빠른지 등껍질이 터지도록 뛰어도 도저히 잡을 수가 없으니 내 신세가 처량하구려…….”</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="26" t="inlineStr">
+        <is>
+          <t>character_Turtle_02</t>
+        </is>
+      </c>
+      <c r="B44" s="25" t="inlineStr">
+        <is>
+          <t>거북이</t>
+        </is>
+      </c>
+      <c r="C44" s="26" t="inlineStr">
+        <is>
+          <t>"……하여 내 조심스레 청하건대, 저 얄미운 토끼 녀석을 음식으로 꼬여내 주지 않겠소? 듣자 하니 녀석이 노릇노릇한 당근전을 자다가도 깰 만큼 좋아한다 하더이다. 내 요청을 들어주어 녀석을 배불리 잠재워만 준다면, 용궁의 이름으로 귀한 보상을 내리겠소!”</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="26" t="inlineStr">
+        <is>
+          <t>character_Rabbit_01</t>
+        </is>
+      </c>
+      <c r="B45" s="25" t="inlineStr">
+        <is>
+          <t>토끼</t>
+        </is>
+      </c>
+      <c r="C45" s="26" t="inlineStr">
+        <is>
+          <t>"백날 뛰어봐야 결과는 뻔한데, 거북이 녀석은 참 미련하기도 하지. 내 발걸음 반의반도 못 따라오면서 용왕님 핑계 대는 것도 이젠 지겹다니까.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="26" t="inlineStr">
+        <is>
+          <t>character_Rabbit_02</t>
+        </is>
+      </c>
+      <c r="B46" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">토끼 </t>
+        </is>
+      </c>
+      <c r="C46" s="26" t="inlineStr">
+        <is>
+          <t>“꼼짝 마! 거북 영감의 얄팍한 수작에 넘어간 모양인데, 다 티 나니까 다가오지 마요. 내 간이 탐난다고 덥석 청을 들어주다니 참 나…….”</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="26" t="inlineStr">
+        <is>
+          <t>character_Rabbit_03</t>
+        </is>
+      </c>
+      <c r="B47" s="25" t="inlineStr">
+        <is>
+          <t>토끼</t>
+        </is>
+      </c>
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>(킁킁, 코를 격하게 씰룩이며) “……음? 잠깐, 이게 무슨 냄새지? 고소하면서도 달콤하고, 기름진 이 완벽한 향은……?!”</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="26" t="inlineStr">
+        <is>
+          <t>character_Rabbit_04</t>
+        </is>
+      </c>
+      <c r="B48" s="25" t="inlineStr">
+        <is>
+          <t>토끼</t>
+        </is>
+      </c>
+      <c r="C48" s="26" t="inlineStr">
+        <is>
+          <t>(침을 꿀꺽 삼키며 짐짓 엄숙하게) “흐, 흥! 거북이 녀석의 꼬임수인 건 알지만…… 음식이 무슨 죄가 있겠어? 정 날 잡고 싶다면, 거기 보이는 나뭇그루터기 위에 그 노릇노릇한 ‘당근전’을 얌전히 올려놓으시지!”</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="26" t="inlineStr">
+        <is>
+          <t>character_Turtle_03</t>
+        </is>
+      </c>
+      <c r="B49" s="25" t="inlineStr">
+        <is>
+          <t>거북이</t>
+        </is>
+      </c>
+      <c r="C49" s="26" t="inlineStr">
+        <is>
+          <t>“허어, 기적이로세! 그 얄미운 토끼 녀석이 저렇게 행복한 표정으로 쿨쿨 잠들다니……! 요리사 양반의 솜씨 덕분에 드디어 용궁의 시름을 덜게 되었소.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="26" t="inlineStr">
+        <is>
+          <t>character_Turtle_04</t>
+        </is>
+      </c>
+      <c r="B50" s="25" t="inlineStr">
+        <is>
+          <t>거북이</t>
+        </is>
+      </c>
+      <c r="C50" s="26" t="inlineStr">
+        <is>
+          <t>“참으로 고맙소. 내 감사의 뜻을 담아, 저 깊은 심해에서만 자라는 신비로운 ‘해산물’을 드리리다. 여정에 큰 보탬이 되기를 바라오.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="26" t="inlineStr">
+        <is>
+          <t>character_YeonSanJa_01</t>
+        </is>
+      </c>
+      <c r="B51" s="25" t="inlineStr">
+        <is>
+          <t>연산자군</t>
+        </is>
+      </c>
+      <c r="C51" s="26" t="inlineStr">
+        <is>
+          <t>“네놈이 감히 요상한 역당 무리를 이끌고 팔도를 누비며 과인의 민심을 어지럽힌다는 그 음식 도적이렷다! 오냐, 내 오늘 마지막 기회를 주마. 당장 과인의 메마른 입맛을 만족시킬 수라를 올려라! 만약 조금이라도 기대를 저버린다면, 네놈의 그 요상한 나무덩이 목줄기는 물론이고, 저 미개한 나무목과 가녀린 춘양의 목까지 모조리 잘라 당장 광화문 거리에 높이 매달 것이다!”</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="26" t="inlineStr">
+        <is>
+          <t>character_YeonSanJa_02</t>
+        </is>
+      </c>
+      <c r="B52" s="25" t="inlineStr">
+        <is>
+          <t>연산자군</t>
+        </is>
+      </c>
+      <c r="C52" s="26" t="inlineStr">
+        <is>
+          <t>“……이, 이 맛은 대체 무엇이란 말이냐? 바다의 깊은 숨결과 산의 정취가 혀끝에서 기어처럼 완벽하게 맞물려 돌아가는구나……! 뜨거운 증기가 온몸의 혈관을 깨우듯, 과인의 막힌 숨통이 트이는구나. 아아…… 내가 그동안 탐욕과 분노라는 차가운 쇠사슬에 묶여 눈이 멀었었구나."</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="26" t="inlineStr">
+        <is>
+          <t>character_YeonSanJa_03</t>
+        </is>
+      </c>
+      <c r="B53" s="25" t="inlineStr">
+        <is>
+          <t>연산자군</t>
+        </is>
+      </c>
+      <c r="C53" s="30" t="inlineStr">
+        <is>
+          <t>"장금과 영심이를 잃은 슬픔에 눈이 멀어 백성들을 짓밟았으니, 참으로 부끄럽도다! 내 마음의 오랜 병이 비로소 씻은 듯이 나았구나!
+여봐라! 오늘부로 온 나라의 가혹한 수탈을 당장 멈추고, 굶주린 백성들이 배불리 먹을 수 있도록 구휼미를 아낌없이 풀 것이다! 자, 파티…… 가 아니라, 조선 팔도가 들썩일 성대한 잔치를 열어라!!”</t>
+        </is>
+      </c>
+    </row>
     <row r="54" ht="15.75" customHeight="1"/>
     <row r="55" ht="15.75" customHeight="1"/>
     <row r="56" ht="15.75" customHeight="1"/>
@@ -2488,8 +2717,7 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/OO_Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Dialogue.xlsx
@@ -362,19 +362,10 @@
     <t>“꼼짝 마! 거북 영감의 얄팍한 수작에 넘어간 모양인데, 다 티 나니까 다가오지 마요. 내 간이 탐난다고 덥석 청을 들어주다니 참 나…….”</t>
   </si>
   <si>
-    <t>character_Rabbit_03</t>
-  </si>
-  <si>
-    <t>(킁킁, 코를 격하게 씰룩이며) “……음? 잠깐, 이게 무슨 냄새지? 고소하면서도 달콤하고, 기름진 이 완벽한 향은……?!”</t>
-  </si>
-  <si>
     <t>character_Rabbit_04</t>
   </si>
   <si>
     <t>(침을 꿀꺽 삼키며 짐짓 엄숙하게) “흐, 흥! 거북이 녀석의 꼬임수인 건 알지만…… 음식이 무슨 죄가 있겠어? 정 날 잡고 싶다면, 거기 보이는 나뭇그루터기 위에 그 노릇노릇한 ‘당근전’을 얌전히 올려놓으시지!”</t>
-  </si>
-  <si>
-    <t>character_Turtle_03</t>
   </si>
   <si>
     <t>“허어, 기적이로세! 그 얄미운 토끼 녀석이 저렇게 행복한 표정으로 쿨쿨 잠들다니……! 요리사 양반의 솜씨 덕분에 드디어 용궁의 시름을 덜게 되었소.”</t>
@@ -413,6 +404,335 @@
   </si>
   <si>
     <t>character_Sangun_03</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>킁킁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>코를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>격하게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>씰룩이며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) “……</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">? </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>잠깐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>무슨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>냄새지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">? </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>고소하면서도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>달콤하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>기름진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>완벽한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>향은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>……?!”</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Rabbit_03</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Turtle_03</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1561,13 +1881,13 @@
     </row>
     <row r="40" spans="1:8" ht="15.75" customHeight="1">
       <c r="A40" s="22" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B40" s="22" t="s">
         <v>95</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D40" s="23"/>
       <c r="E40" s="23"/>
@@ -1647,79 +1967,79 @@
     </row>
     <row r="47" spans="1:8" ht="15.75" customHeight="1">
       <c r="A47" s="20" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="B47" s="19" t="s">
         <v>110</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="15.75" customHeight="1">
       <c r="A48" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B48" s="19" t="s">
         <v>110</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="15.75" customHeight="1">
       <c r="A49" s="20" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="B49" s="19" t="s">
         <v>105</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="15.75" customHeight="1">
       <c r="A50" s="20" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B50" s="19" t="s">
         <v>105</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="15.75" customHeight="1">
       <c r="A51" s="20" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B51" s="19" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="15.75" customHeight="1">
       <c r="A52" s="20" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B52" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="C52" s="20" t="s">
         <v>124</v>
-      </c>
-      <c r="C52" s="20" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="15.75" customHeight="1">
       <c r="A53" s="20" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C53" s="24" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="15.75" customHeight="1"/>
